--- a/cambios_tinacode.xlsx
+++ b/cambios_tinacode.xlsx
@@ -105,7 +105,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001565C0"/>
+        <fgColor rgb="00546E7A"/>
       </patternFill>
     </fill>
     <fill>
@@ -115,7 +115,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00546E7A"/>
+        <fgColor rgb="001565C0"/>
       </patternFill>
     </fill>
     <fill>
@@ -581,7 +581,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F97"/>
+  <dimension ref="A1:F96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -664,158 +664,158 @@
       </c>
     </row>
     <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Mié</t>
+        </is>
+      </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
+          <t>Mantenimiento</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>implementacion external_contacts</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr"/>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>Gerardo Herrera</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>Mantenimiento</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>Revert "implementacion correos externos"</t>
+        </is>
+      </c>
+      <c r="E5" s="10" t="inlineStr"/>
+      <c r="F5" s="11" t="inlineStr">
+        <is>
+          <t>Gerardo Herrera</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>Mantenimiento</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>implementacion correos externos</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr"/>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>Gerardo Herrera</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>Mantenimiento</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>implementacion de icono mediante AI</t>
+        </is>
+      </c>
+      <c r="E7" s="10" t="inlineStr"/>
+      <c r="F7" s="11" t="inlineStr">
+        <is>
+          <t>Gerardo Herrera</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Jue</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
           <t>Nueva función</t>
         </is>
       </c>
-      <c r="D4" s="9" t="inlineStr">
-        <is>
-          <t>prompts enriquecidos + hover info en cards + scripts utilitarios</t>
-        </is>
-      </c>
-      <c r="E4" s="10" t="inlineStr">
-        <is>
-          <t>AI</t>
-        </is>
-      </c>
-      <c r="F4" s="11" t="inlineStr">
-        <is>
-          <t>Isaac Medina</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>Mié</t>
-        </is>
-      </c>
-      <c r="C5" s="12" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>implementacion external_contacts</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="inlineStr"/>
-      <c r="F5" s="7" t="inlineStr">
-        <is>
-          <t>Gerardo Herrera</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="18" customHeight="1">
-      <c r="C6" s="12" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
-        </is>
-      </c>
-      <c r="D6" s="9" t="inlineStr">
-        <is>
-          <t>Revert "implementacion correos externos"</t>
-        </is>
-      </c>
-      <c r="E6" s="10" t="inlineStr"/>
-      <c r="F6" s="11" t="inlineStr">
-        <is>
-          <t>Gerardo Herrera</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="C7" s="12" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>implementacion correos externos</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr"/>
-      <c r="F7" s="7" t="inlineStr">
-        <is>
-          <t>Gerardo Herrera</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="18" customHeight="1">
-      <c r="C8" s="12" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
-        </is>
-      </c>
-      <c r="D8" s="9" t="inlineStr">
-        <is>
-          <t>implementacion de icono mediante AI</t>
-        </is>
-      </c>
-      <c r="E8" s="10" t="inlineStr"/>
-      <c r="F8" s="11" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>ampliar paleta de colores de tarjetas de 8 a 16 gradientes</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>Gerardo Herrera</t>
         </is>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>Jue</t>
-        </is>
-      </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="C9" s="12" t="inlineStr">
         <is>
           <t>Nueva función</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>ampliar paleta de colores de tarjetas de 8 a 16 gradientes</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
-      <c r="F9" s="7" t="inlineStr">
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>remover fondo blanco con sharp para generar PNGs transparentes</t>
+        </is>
+      </c>
+      <c r="E9" s="10" t="inlineStr">
+        <is>
+          <t>ICONS</t>
+        </is>
+      </c>
+      <c r="F9" s="11" t="inlineStr">
         <is>
           <t>Gerardo Herrera</t>
         </is>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="12" t="inlineStr">
         <is>
           <t>Nueva función</t>
         </is>
       </c>
-      <c r="D10" s="9" t="inlineStr">
-        <is>
-          <t>remover fondo blanco con sharp para generar PNGs transparentes</t>
-        </is>
-      </c>
-      <c r="E10" s="10" t="inlineStr">
-        <is>
-          <t>ICONS</t>
-        </is>
-      </c>
-      <c r="F10" s="11" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>mostrar apps propias en tinaStore para administradores</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>CATALOG</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>Gerardo Herrera</t>
         </is>
@@ -824,108 +824,108 @@
     <row r="11" ht="18" customHeight="1">
       <c r="C11" s="8" t="inlineStr">
         <is>
+          <t>Mantenimiento</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>Se modifica administrador</t>
+        </is>
+      </c>
+      <c r="E11" s="10" t="inlineStr">
+        <is>
+          <t>SCRIPT</t>
+        </is>
+      </c>
+      <c r="F11" s="11" t="inlineStr">
+        <is>
+          <t>Gerardo Herrera</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>Mantenimiento</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>se agrega administrador</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>SCRIPTS</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>Gerardo Herrera</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="C13" s="13" t="inlineStr">
+        <is>
+          <t>Corrección</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>actualizar botón a éxito al terminar publicación</t>
+        </is>
+      </c>
+      <c r="E13" s="10" t="inlineStr">
+        <is>
+          <t>PUBLISH</t>
+        </is>
+      </c>
+      <c r="F13" s="11" t="inlineStr">
+        <is>
+          <t>Gerardo Herrera</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="C14" s="12" t="inlineStr">
+        <is>
           <t>Nueva función</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>mostrar apps propias en tinaStore para administradores</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="inlineStr">
-        <is>
-          <t>CATALOG</t>
-        </is>
-      </c>
-      <c r="F11" s="7" t="inlineStr">
-        <is>
-          <t>Gerardo Herrera</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="18" customHeight="1">
-      <c r="C12" s="12" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
-        </is>
-      </c>
-      <c r="D12" s="9" t="inlineStr">
-        <is>
-          <t>Se modifica administrador</t>
-        </is>
-      </c>
-      <c r="E12" s="10" t="inlineStr">
-        <is>
-          <t>SCRIPT</t>
-        </is>
-      </c>
-      <c r="F12" s="11" t="inlineStr">
-        <is>
-          <t>Gerardo Herrera</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="18" customHeight="1">
-      <c r="C13" s="12" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>se agrega administrador</t>
-        </is>
-      </c>
-      <c r="E13" s="6" t="inlineStr">
-        <is>
-          <t>SCRIPTS</t>
-        </is>
-      </c>
-      <c r="F13" s="7" t="inlineStr">
-        <is>
-          <t>Gerardo Herrera</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="18" customHeight="1">
-      <c r="C14" s="13" t="inlineStr">
-        <is>
-          <t>Corrección</t>
-        </is>
-      </c>
-      <c r="D14" s="9" t="inlineStr">
-        <is>
-          <t>actualizar botón a éxito al terminar publicación</t>
-        </is>
-      </c>
-      <c r="E14" s="10" t="inlineStr">
-        <is>
-          <t>PUBLISH</t>
-        </is>
-      </c>
-      <c r="F14" s="11" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>cambiar fondo de iconos a transparente</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>ICONS</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
         <is>
           <t>Gerardo Herrera</t>
         </is>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="C15" s="8" t="inlineStr">
-        <is>
-          <t>Nueva función</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>cambiar fondo de iconos a transparente</t>
-        </is>
-      </c>
-      <c r="E15" s="6" t="inlineStr">
+      <c r="C15" s="13" t="inlineStr">
+        <is>
+          <t>Corrección</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>corregir nombre de modelo a gemini-2.5-flash-image</t>
+        </is>
+      </c>
+      <c r="E15" s="10" t="inlineStr">
         <is>
           <t>ICONS</t>
         </is>
       </c>
-      <c r="F15" s="7" t="inlineStr">
+      <c r="F15" s="11" t="inlineStr">
         <is>
           <t>Gerardo Herrera</t>
         </is>
@@ -937,17 +937,17 @@
           <t>Corrección</t>
         </is>
       </c>
-      <c r="D16" s="9" t="inlineStr">
-        <is>
-          <t>corregir nombre de modelo a gemini-2.5-flash-image</t>
-        </is>
-      </c>
-      <c r="E16" s="10" t="inlineStr">
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>migrar generación de iconos a @google/genai y servir desde CDN en staging</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
         <is>
           <t>ICONS</t>
         </is>
       </c>
-      <c r="F16" s="11" t="inlineStr">
+      <c r="F16" s="7" t="inlineStr">
         <is>
           <t>Gerardo Herrera</t>
         </is>
@@ -959,17 +959,17 @@
           <t>Corrección</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>migrar generación de iconos a @google/genai y servir desde CDN en staging</t>
-        </is>
-      </c>
-      <c r="E17" s="6" t="inlineStr">
-        <is>
-          <t>ICONS</t>
-        </is>
-      </c>
-      <c r="F17" s="7" t="inlineStr">
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>Inicio de session para correos externos</t>
+        </is>
+      </c>
+      <c r="E17" s="10" t="inlineStr">
+        <is>
+          <t>CORREOSEXTERNOS</t>
+        </is>
+      </c>
+      <c r="F17" s="11" t="inlineStr">
         <is>
           <t>Gerardo Herrera</t>
         </is>
@@ -981,17 +981,17 @@
           <t>Corrección</t>
         </is>
       </c>
-      <c r="D18" s="9" t="inlineStr">
-        <is>
-          <t>Inicio de session para correos externos</t>
-        </is>
-      </c>
-      <c r="E18" s="10" t="inlineStr">
-        <is>
-          <t>CORREOSEXTERNOS</t>
-        </is>
-      </c>
-      <c r="F18" s="11" t="inlineStr">
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>Correcion en guardado de respuesta gemini</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>ICON</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
         <is>
           <t>Gerardo Herrera</t>
         </is>
@@ -1003,17 +1003,17 @@
           <t>Corrección</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
-        <is>
-          <t>Correcion en guardado de respuesta gemini</t>
-        </is>
-      </c>
-      <c r="E19" s="6" t="inlineStr">
-        <is>
-          <t>ICON</t>
-        </is>
-      </c>
-      <c r="F19" s="7" t="inlineStr">
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>configuracion en genini-2.0-flas para mostrar icono y guardado en bucket</t>
+        </is>
+      </c>
+      <c r="E19" s="10" t="inlineStr">
+        <is>
+          <t>ICONS</t>
+        </is>
+      </c>
+      <c r="F19" s="11" t="inlineStr">
         <is>
           <t>Gerardo Herrera</t>
         </is>
@@ -1025,17 +1025,17 @@
           <t>Corrección</t>
         </is>
       </c>
-      <c r="D20" s="9" t="inlineStr">
-        <is>
-          <t>configuracion en genini-2.0-flas para mostrar icono y guardado en bucket</t>
-        </is>
-      </c>
-      <c r="E20" s="10" t="inlineStr">
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>migrar generación de iconos de Imagen 2 a Gemini 2.0 Flash</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
         <is>
           <t>ICONS</t>
         </is>
       </c>
-      <c r="F20" s="11" t="inlineStr">
+      <c r="F20" s="7" t="inlineStr">
         <is>
           <t>Gerardo Herrera</t>
         </is>
@@ -1047,93 +1047,93 @@
           <t>Corrección</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
-        <is>
-          <t>migrar generación de iconos de Imagen 2 a Gemini 2.0 Flash</t>
-        </is>
-      </c>
-      <c r="E21" s="6" t="inlineStr">
+      <c r="D21" s="9" t="inlineStr">
+        <is>
+          <t>corregir validación de token en magic links</t>
+        </is>
+      </c>
+      <c r="E21" s="10" t="inlineStr">
+        <is>
+          <t>EXTERNAL_CONTACTS</t>
+        </is>
+      </c>
+      <c r="F21" s="11" t="inlineStr">
+        <is>
+          <t>Gerardo Herrera</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="C22" s="12" t="inlineStr">
+        <is>
+          <t>Nueva función</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>refactorizar Lista de Consejo con acceso restringido</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>EXTERNAL_CONTACTS</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>Gerardo Herrera</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>Vie</t>
+        </is>
+      </c>
+      <c r="C23" s="13" t="inlineStr">
+        <is>
+          <t>Corrección</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>Correcion tamaño Spotlight</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>IU</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>Gerardo Herrera</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="C24" s="13" t="inlineStr">
+        <is>
+          <t>Corrección</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="inlineStr">
+        <is>
+          <t>Incrementando paleta de colores para la generacion de iconos</t>
+        </is>
+      </c>
+      <c r="E24" s="10" t="inlineStr">
         <is>
           <t>ICONS</t>
         </is>
       </c>
-      <c r="F21" s="7" t="inlineStr">
-        <is>
-          <t>Gerardo Herrera</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="18" customHeight="1">
-      <c r="C22" s="13" t="inlineStr">
-        <is>
-          <t>Corrección</t>
-        </is>
-      </c>
-      <c r="D22" s="9" t="inlineStr">
-        <is>
-          <t>corregir validación de token en magic links</t>
-        </is>
-      </c>
-      <c r="E22" s="10" t="inlineStr">
-        <is>
-          <t>EXTERNAL_CONTACTS</t>
-        </is>
-      </c>
-      <c r="F22" s="11" t="inlineStr">
-        <is>
-          <t>Gerardo Herrera</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="18" customHeight="1">
-      <c r="C23" s="8" t="inlineStr">
-        <is>
-          <t>Nueva función</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="inlineStr">
-        <is>
-          <t>refactorizar Lista de Consejo con acceso restringido</t>
-        </is>
-      </c>
-      <c r="E23" s="6" t="inlineStr">
-        <is>
-          <t>EXTERNAL_CONTACTS</t>
-        </is>
-      </c>
-      <c r="F23" s="7" t="inlineStr">
-        <is>
-          <t>Gerardo Herrera</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>Vie</t>
-        </is>
-      </c>
-      <c r="C24" s="13" t="inlineStr">
-        <is>
-          <t>Corrección</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="inlineStr">
-        <is>
-          <t>Correcion tamaño Spotlight</t>
-        </is>
-      </c>
-      <c r="E24" s="6" t="inlineStr">
-        <is>
-          <t>IU</t>
-        </is>
-      </c>
-      <c r="F24" s="7" t="inlineStr">
+      <c r="F24" s="11" t="inlineStr">
         <is>
           <t>Gerardo Herrera</t>
         </is>
@@ -1145,17 +1145,17 @@
           <t>Corrección</t>
         </is>
       </c>
-      <c r="D25" s="9" t="inlineStr">
-        <is>
-          <t>Incrementando paleta de colores para la generacion de iconos</t>
-        </is>
-      </c>
-      <c r="E25" s="10" t="inlineStr">
-        <is>
-          <t>ICONS</t>
-        </is>
-      </c>
-      <c r="F25" s="11" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>Previene que se guarden app duplicadas</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>BAKEND</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="inlineStr">
         <is>
           <t>Gerardo Herrera</t>
         </is>
@@ -1167,269 +1167,269 @@
           <t>Corrección</t>
         </is>
       </c>
-      <c r="D26" s="5" t="inlineStr">
-        <is>
-          <t>Previene que se guarden app duplicadas</t>
-        </is>
-      </c>
-      <c r="E26" s="6" t="inlineStr">
-        <is>
-          <t>BAKEND</t>
-        </is>
-      </c>
-      <c r="F26" s="7" t="inlineStr">
+      <c r="D26" s="9" t="inlineStr">
+        <is>
+          <t>Correccion Shimmer</t>
+        </is>
+      </c>
+      <c r="E26" s="10" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="F26" s="11" t="inlineStr">
         <is>
           <t>Gerardo Herrera</t>
         </is>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
-      <c r="C27" s="13" t="inlineStr">
-        <is>
-          <t>Corrección</t>
-        </is>
-      </c>
-      <c r="D27" s="9" t="inlineStr">
-        <is>
-          <t>Correccion Shimmer</t>
-        </is>
-      </c>
-      <c r="E27" s="10" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
-      <c r="F27" s="11" t="inlineStr">
+      <c r="C27" s="12" t="inlineStr">
+        <is>
+          <t>Nueva función</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>shimmer en iconos IA con fade-in y fallback</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="inlineStr">
         <is>
           <t>Gerardo Herrera</t>
         </is>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
-      <c r="C28" s="8" t="inlineStr">
+      <c r="C28" s="12" t="inlineStr">
         <is>
           <t>Nueva función</t>
         </is>
       </c>
-      <c r="D28" s="5" t="inlineStr">
-        <is>
-          <t>shimmer en iconos IA con fade-in y fallback</t>
-        </is>
-      </c>
-      <c r="E28" s="6" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
-      <c r="F28" s="7" t="inlineStr">
+      <c r="D28" s="9" t="inlineStr">
+        <is>
+          <t>cambiar promt de generacion de icono tipo sticker sin textos</t>
+        </is>
+      </c>
+      <c r="E28" s="10" t="inlineStr">
+        <is>
+          <t>ICONS</t>
+        </is>
+      </c>
+      <c r="F28" s="11" t="inlineStr">
         <is>
           <t>Gerardo Herrera</t>
         </is>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
-      <c r="C29" s="8" t="inlineStr">
+      <c r="C29" s="12" t="inlineStr">
         <is>
           <t>Nueva función</t>
         </is>
       </c>
-      <c r="D29" s="9" t="inlineStr">
-        <is>
-          <t>cambiar promt de generacion de icono tipo sticker sin textos</t>
-        </is>
-      </c>
-      <c r="E29" s="10" t="inlineStr">
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>cambiar promt de generacion de icono tipo sticker con bordes</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="inlineStr">
         <is>
           <t>ICONS</t>
         </is>
       </c>
-      <c r="F29" s="11" t="inlineStr">
+      <c r="F29" s="7" t="inlineStr">
         <is>
           <t>Gerardo Herrera</t>
         </is>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
-      <c r="C30" s="8" t="inlineStr">
+      <c r="C30" s="12" t="inlineStr">
         <is>
           <t>Nueva función</t>
         </is>
       </c>
-      <c r="D30" s="5" t="inlineStr">
-        <is>
-          <t>cambiar promt de generacion de icono tipo sticker con bordes</t>
-        </is>
-      </c>
-      <c r="E30" s="6" t="inlineStr">
+      <c r="D30" s="9" t="inlineStr">
+        <is>
+          <t>cambiar promt de generacion de icono tipo sticker</t>
+        </is>
+      </c>
+      <c r="E30" s="10" t="inlineStr">
         <is>
           <t>ICONS</t>
         </is>
       </c>
-      <c r="F30" s="7" t="inlineStr">
+      <c r="F30" s="11" t="inlineStr">
         <is>
           <t>Gerardo Herrera</t>
         </is>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
-      <c r="C31" s="8" t="inlineStr">
+      <c r="C31" s="12" t="inlineStr">
         <is>
           <t>Nueva función</t>
         </is>
       </c>
-      <c r="D31" s="9" t="inlineStr">
-        <is>
-          <t>cambiar promt de generacion de icono tipo sticker</t>
-        </is>
-      </c>
-      <c r="E31" s="10" t="inlineStr">
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>cambiar promt de generacion de icono tipo 3D</t>
+        </is>
+      </c>
+      <c r="E31" s="6" t="inlineStr">
         <is>
           <t>ICONS</t>
         </is>
       </c>
-      <c r="F31" s="11" t="inlineStr">
+      <c r="F31" s="7" t="inlineStr">
         <is>
           <t>Gerardo Herrera</t>
         </is>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
-      <c r="C32" s="8" t="inlineStr">
+      <c r="C32" s="13" t="inlineStr">
+        <is>
+          <t>Corrección</t>
+        </is>
+      </c>
+      <c r="D32" s="9" t="inlineStr">
+        <is>
+          <t>limitar ancho máximo de sp-apps a 750px</t>
+        </is>
+      </c>
+      <c r="E32" s="10" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="F32" s="11" t="inlineStr">
+        <is>
+          <t>Gerardo Herrera</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="18" customHeight="1">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>Lun</t>
+        </is>
+      </c>
+      <c r="C33" s="13" t="inlineStr">
+        <is>
+          <t>Corrección</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>simplifica textos de pasos de deploy para mejor legibilidad</t>
+        </is>
+      </c>
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t>I18N</t>
+        </is>
+      </c>
+      <c r="F33" s="7" t="inlineStr">
+        <is>
+          <t>Gerardo Herrera</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="C34" s="12" t="inlineStr">
         <is>
           <t>Nueva función</t>
         </is>
       </c>
-      <c r="D32" s="5" t="inlineStr">
-        <is>
-          <t>cambiar promt de generacion de icono tipo 3D</t>
-        </is>
-      </c>
-      <c r="E32" s="6" t="inlineStr">
-        <is>
-          <t>ICONS</t>
-        </is>
-      </c>
-      <c r="F32" s="7" t="inlineStr">
-        <is>
-          <t>Gerardo Herrera</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="18" customHeight="1">
-      <c r="C33" s="13" t="inlineStr">
-        <is>
-          <t>Corrección</t>
-        </is>
-      </c>
-      <c r="D33" s="9" t="inlineStr">
-        <is>
-          <t>limitar ancho máximo de sp-apps a 750px</t>
-        </is>
-      </c>
-      <c r="E33" s="10" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
-      <c r="F33" s="11" t="inlineStr">
-        <is>
-          <t>Gerardo Herrera</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="18" customHeight="1">
-      <c r="A34" s="3" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="B34" s="3" t="inlineStr">
-        <is>
-          <t>Lun</t>
-        </is>
-      </c>
-      <c r="C34" s="13" t="inlineStr">
-        <is>
-          <t>Corrección</t>
-        </is>
-      </c>
-      <c r="D34" s="5" t="inlineStr">
-        <is>
-          <t>simplifica textos de pasos de deploy para mejor legibilidad</t>
-        </is>
-      </c>
-      <c r="E34" s="6" t="inlineStr">
+      <c r="D34" s="9" t="inlineStr">
+        <is>
+          <t>traduce pasos de deploy progress al idioma activo</t>
+        </is>
+      </c>
+      <c r="E34" s="10" t="inlineStr">
         <is>
           <t>I18N</t>
         </is>
       </c>
-      <c r="F34" s="7" t="inlineStr">
+      <c r="F34" s="11" t="inlineStr">
         <is>
           <t>Gerardo Herrera</t>
         </is>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
-      <c r="C35" s="8" t="inlineStr">
+      <c r="C35" s="13" t="inlineStr">
+        <is>
+          <t>Corrección</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>reemplaza alert() por fieldError/showToast en deploy y updateApp</t>
+        </is>
+      </c>
+      <c r="E35" s="6" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="inlineStr">
+        <is>
+          <t>Gerardo Herrera</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="18" customHeight="1">
+      <c r="C36" s="12" t="inlineStr">
         <is>
           <t>Nueva función</t>
         </is>
       </c>
-      <c r="D35" s="9" t="inlineStr">
-        <is>
-          <t>traduce pasos de deploy progress al idioma activo</t>
-        </is>
-      </c>
-      <c r="E35" s="10" t="inlineStr">
-        <is>
-          <t>I18N</t>
-        </is>
-      </c>
-      <c r="F35" s="11" t="inlineStr">
-        <is>
-          <t>Gerardo Herrera</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="18" customHeight="1">
-      <c r="C36" s="13" t="inlineStr">
-        <is>
-          <t>Corrección</t>
-        </is>
-      </c>
-      <c r="D36" s="5" t="inlineStr">
-        <is>
-          <t>reemplaza alert() por fieldError/showToast en deploy y updateApp</t>
-        </is>
-      </c>
-      <c r="E36" s="6" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
-      <c r="F36" s="7" t="inlineStr">
+      <c r="D36" s="9" t="inlineStr">
+        <is>
+          <t>Reemplaza log de terminal con notificaciones toast de progreso</t>
+        </is>
+      </c>
+      <c r="E36" s="10" t="inlineStr">
+        <is>
+          <t>PUBLISH</t>
+        </is>
+      </c>
+      <c r="F36" s="11" t="inlineStr">
         <is>
           <t>Gerardo Herrera</t>
         </is>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
-      <c r="C37" s="8" t="inlineStr">
-        <is>
-          <t>Nueva función</t>
-        </is>
-      </c>
-      <c r="D37" s="9" t="inlineStr">
-        <is>
-          <t>Reemplaza log de terminal con notificaciones toast de progreso</t>
-        </is>
-      </c>
-      <c r="E37" s="10" t="inlineStr">
-        <is>
-          <t>PUBLISH</t>
-        </is>
-      </c>
-      <c r="F37" s="11" t="inlineStr">
+      <c r="C37" s="13" t="inlineStr">
+        <is>
+          <t>Corrección</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>Actualiza lista de contactos externos permitidos</t>
+        </is>
+      </c>
+      <c r="E37" s="6" t="inlineStr">
+        <is>
+          <t>AUTH</t>
+        </is>
+      </c>
+      <c r="F37" s="7" t="inlineStr">
         <is>
           <t>Gerardo Herrera</t>
         </is>
@@ -1441,17 +1441,17 @@
           <t>Corrección</t>
         </is>
       </c>
-      <c r="D38" s="5" t="inlineStr">
-        <is>
-          <t>Actualiza lista de contactos externos permitidos</t>
-        </is>
-      </c>
-      <c r="E38" s="6" t="inlineStr">
-        <is>
-          <t>AUTH</t>
-        </is>
-      </c>
-      <c r="F38" s="7" t="inlineStr">
+      <c r="D38" s="9" t="inlineStr">
+        <is>
+          <t>Corrige botón Abrir en Mis Apps y Publicar App para apps hasExternal</t>
+        </is>
+      </c>
+      <c r="E38" s="10" t="inlineStr">
+        <is>
+          <t>MYAPPS</t>
+        </is>
+      </c>
+      <c r="F38" s="11" t="inlineStr">
         <is>
           <t>Gerardo Herrera</t>
         </is>
@@ -1463,17 +1463,17 @@
           <t>Corrección</t>
         </is>
       </c>
-      <c r="D39" s="9" t="inlineStr">
-        <is>
-          <t>Corrige botón Abrir en Mis Apps y Publicar App para apps hasExternal</t>
-        </is>
-      </c>
-      <c r="E39" s="10" t="inlineStr">
-        <is>
-          <t>MYAPPS</t>
-        </is>
-      </c>
-      <c r="F39" s="11" t="inlineStr">
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>Corrige acceso a apps hasExternal para usuarios Rotoplas y robustez del login</t>
+        </is>
+      </c>
+      <c r="E39" s="6" t="inlineStr">
+        <is>
+          <t>AUTH</t>
+        </is>
+      </c>
+      <c r="F39" s="7" t="inlineStr">
         <is>
           <t>Gerardo Herrera</t>
         </is>
@@ -1485,61 +1485,61 @@
           <t>Corrección</t>
         </is>
       </c>
-      <c r="D40" s="5" t="inlineStr">
-        <is>
-          <t>Corrige acceso a apps hasExternal para usuarios Rotoplas y robustez del login</t>
-        </is>
-      </c>
-      <c r="E40" s="6" t="inlineStr">
+      <c r="D40" s="9" t="inlineStr">
+        <is>
+          <t>Solo agrega ?t=token a la URL para usuarios externos, no para @rotoplas.com</t>
+        </is>
+      </c>
+      <c r="E40" s="10" t="inlineStr">
         <is>
           <t>AUTH</t>
         </is>
       </c>
-      <c r="F40" s="7" t="inlineStr">
+      <c r="F40" s="11" t="inlineStr">
         <is>
           <t>Gerardo Herrera</t>
         </is>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
-      <c r="C41" s="13" t="inlineStr">
-        <is>
-          <t>Corrección</t>
-        </is>
-      </c>
-      <c r="D41" s="9" t="inlineStr">
-        <is>
-          <t>Solo agrega ?t=token a la URL para usuarios externos, no para @rotoplas.com</t>
-        </is>
-      </c>
-      <c r="E41" s="10" t="inlineStr">
+      <c r="C41" s="12" t="inlineStr">
+        <is>
+          <t>Nueva función</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>Permite login a contactos externos definidos en EXTERNAL_CONTACTS</t>
+        </is>
+      </c>
+      <c r="E41" s="6" t="inlineStr">
         <is>
           <t>AUTH</t>
         </is>
       </c>
-      <c r="F41" s="11" t="inlineStr">
+      <c r="F41" s="7" t="inlineStr">
         <is>
           <t>Gerardo Herrera</t>
         </is>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
-      <c r="C42" s="8" t="inlineStr">
-        <is>
-          <t>Nueva función</t>
-        </is>
-      </c>
-      <c r="D42" s="5" t="inlineStr">
-        <is>
-          <t>Permite login a contactos externos definidos en EXTERNAL_CONTACTS</t>
-        </is>
-      </c>
-      <c r="E42" s="6" t="inlineStr">
-        <is>
-          <t>AUTH</t>
-        </is>
-      </c>
-      <c r="F42" s="7" t="inlineStr">
+      <c r="C42" s="13" t="inlineStr">
+        <is>
+          <t>Corrección</t>
+        </is>
+      </c>
+      <c r="D42" s="9" t="inlineStr">
+        <is>
+          <t>Elimina punto y coma que rompía if/else en renderCatalogSpotlight</t>
+        </is>
+      </c>
+      <c r="E42" s="10" t="inlineStr">
+        <is>
+          <t>SYNTAX</t>
+        </is>
+      </c>
+      <c r="F42" s="11" t="inlineStr">
         <is>
           <t>Gerardo Herrera</t>
         </is>
@@ -1551,17 +1551,17 @@
           <t>Corrección</t>
         </is>
       </c>
-      <c r="D43" s="9" t="inlineStr">
-        <is>
-          <t>Elimina punto y coma que rompía if/else en renderCatalogSpotlight</t>
-        </is>
-      </c>
-      <c r="E43" s="10" t="inlineStr">
-        <is>
-          <t>SYNTAX</t>
-        </is>
-      </c>
-      <c r="F43" s="11" t="inlineStr">
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>Agrega ?t=userToken a la URL al abrir apps con acceso externo</t>
+        </is>
+      </c>
+      <c r="E43" s="6" t="inlineStr">
+        <is>
+          <t>CATALOG</t>
+        </is>
+      </c>
+      <c r="F43" s="7" t="inlineStr">
         <is>
           <t>Gerardo Herrera</t>
         </is>
@@ -1573,127 +1573,127 @@
           <t>Corrección</t>
         </is>
       </c>
-      <c r="D44" s="5" t="inlineStr">
-        <is>
-          <t>Agrega ?t=userToken a la URL al abrir apps con acceso externo</t>
-        </is>
-      </c>
-      <c r="E44" s="6" t="inlineStr">
-        <is>
-          <t>CATALOG</t>
-        </is>
-      </c>
-      <c r="F44" s="7" t="inlineStr">
+      <c r="D44" s="9" t="inlineStr">
+        <is>
+          <t>Usuarios Rotoplas siempre van al flujo normal aunque abran un share link</t>
+        </is>
+      </c>
+      <c r="E44" s="10" t="inlineStr">
+        <is>
+          <t>SHARE</t>
+        </is>
+      </c>
+      <c r="F44" s="11" t="inlineStr">
         <is>
           <t>Gerardo Herrera</t>
         </is>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
-      <c r="C45" s="13" t="inlineStr">
-        <is>
-          <t>Corrección</t>
-        </is>
-      </c>
-      <c r="D45" s="9" t="inlineStr">
-        <is>
-          <t>Usuarios Rotoplas siempre van al flujo normal aunque abran un share link</t>
-        </is>
-      </c>
-      <c r="E45" s="10" t="inlineStr">
+      <c r="C45" s="12" t="inlineStr">
+        <is>
+          <t>Nueva función</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>Links de invitación públicos para compartir apps sin login</t>
+        </is>
+      </c>
+      <c r="E45" s="6" t="inlineStr">
         <is>
           <t>SHARE</t>
         </is>
       </c>
-      <c r="F45" s="11" t="inlineStr">
+      <c r="F45" s="7" t="inlineStr">
         <is>
           <t>Gerardo Herrera</t>
         </is>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
-      <c r="C46" s="8" t="inlineStr">
+      <c r="C46" s="13" t="inlineStr">
+        <is>
+          <t>Corrección</t>
+        </is>
+      </c>
+      <c r="D46" s="9" t="inlineStr">
+        <is>
+          <t>Extiende CSS de tarjetas de catálogo a sección Favoritas</t>
+        </is>
+      </c>
+      <c r="E46" s="10" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="F46" s="11" t="inlineStr">
+        <is>
+          <t>Gerardo Herrera</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="18" customHeight="1">
+      <c r="C47" s="14" t="inlineStr">
+        <is>
+          <t>Refactorización</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>Extrae makeCatalogCard para unificar render en Favoritas y Catálogo</t>
+        </is>
+      </c>
+      <c r="E47" s="6" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="F47" s="7" t="inlineStr">
+        <is>
+          <t>Gerardo Herrera</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="18" customHeight="1">
+      <c r="C48" s="12" t="inlineStr">
         <is>
           <t>Nueva función</t>
         </is>
       </c>
-      <c r="D46" s="5" t="inlineStr">
-        <is>
-          <t>Links de invitación públicos para compartir apps sin login</t>
-        </is>
-      </c>
-      <c r="E46" s="6" t="inlineStr">
-        <is>
-          <t>SHARE</t>
-        </is>
-      </c>
-      <c r="F46" s="7" t="inlineStr">
-        <is>
-          <t>Gerardo Herrera</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="18" customHeight="1">
-      <c r="C47" s="13" t="inlineStr">
-        <is>
-          <t>Corrección</t>
-        </is>
-      </c>
-      <c r="D47" s="9" t="inlineStr">
-        <is>
-          <t>Extiende CSS de tarjetas de catálogo a sección Favoritas</t>
-        </is>
-      </c>
-      <c r="E47" s="10" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
-      <c r="F47" s="11" t="inlineStr">
-        <is>
-          <t>Gerardo Herrera</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="18" customHeight="1">
-      <c r="C48" s="14" t="inlineStr">
-        <is>
-          <t>Refactorización</t>
-        </is>
-      </c>
-      <c r="D48" s="5" t="inlineStr">
-        <is>
-          <t>Extrae makeCatalogCard para unificar render en Favoritas y Catálogo</t>
-        </is>
-      </c>
-      <c r="E48" s="6" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
-      <c r="F48" s="7" t="inlineStr">
+      <c r="D48" s="9" t="inlineStr">
+        <is>
+          <t>Apps favoritas con localStorage, boton estrella y seccion en sidebar</t>
+        </is>
+      </c>
+      <c r="E48" s="10" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="F48" s="11" t="inlineStr">
         <is>
           <t>Gerardo Herrera</t>
         </is>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
-      <c r="C49" s="8" t="inlineStr">
-        <is>
-          <t>Nueva función</t>
-        </is>
-      </c>
-      <c r="D49" s="9" t="inlineStr">
-        <is>
-          <t>Apps favoritas con localStorage, boton estrella y seccion en sidebar</t>
-        </is>
-      </c>
-      <c r="E49" s="10" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
-      <c r="F49" s="11" t="inlineStr">
+      <c r="C49" s="13" t="inlineStr">
+        <is>
+          <t>Corrección</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>Tooltip flotante usa CSS variables para adaptarse a tema claro/oscuro</t>
+        </is>
+      </c>
+      <c r="E49" s="6" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="F49" s="7" t="inlineStr">
         <is>
           <t>Gerardo Herrera</t>
         </is>
@@ -1705,181 +1705,181 @@
           <t>Corrección</t>
         </is>
       </c>
-      <c r="D50" s="5" t="inlineStr">
-        <is>
-          <t>Tooltip flotante usa CSS variables para adaptarse a tema claro/oscuro</t>
-        </is>
-      </c>
-      <c r="E50" s="6" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
-      <c r="F50" s="7" t="inlineStr">
+      <c r="D50" s="9" t="inlineStr">
+        <is>
+          <t>Delay 300ms antes de mostrar tooltip de catalog-card</t>
+        </is>
+      </c>
+      <c r="E50" s="10" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="F50" s="11" t="inlineStr">
         <is>
           <t>Gerardo Herrera</t>
         </is>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
-      <c r="C51" s="13" t="inlineStr">
-        <is>
-          <t>Corrección</t>
-        </is>
-      </c>
-      <c r="D51" s="9" t="inlineStr">
-        <is>
-          <t>Delay 300ms antes de mostrar tooltip de catalog-card</t>
-        </is>
-      </c>
-      <c r="E51" s="10" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
-      <c r="F51" s="11" t="inlineStr">
+      <c r="C51" s="12" t="inlineStr">
+        <is>
+          <t>Nueva función</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>Tooltip flotante para aiDescription en catalog-card</t>
+        </is>
+      </c>
+      <c r="E51" s="6" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="F51" s="7" t="inlineStr">
         <is>
           <t>Gerardo Herrera</t>
         </is>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
-      <c r="C52" s="8" t="inlineStr">
+      <c r="C52" s="13" t="inlineStr">
+        <is>
+          <t>Corrección</t>
+        </is>
+      </c>
+      <c r="D52" s="9" t="inlineStr">
+        <is>
+          <t>Toast confirm en top, mensaje de confirmacion actualizado</t>
+        </is>
+      </c>
+      <c r="E52" s="10" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="F52" s="11" t="inlineStr">
+        <is>
+          <t>Gerardo Herrera</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="18" customHeight="1">
+      <c r="C53" s="12" t="inlineStr">
         <is>
           <t>Nueva función</t>
         </is>
       </c>
-      <c r="D52" s="5" t="inlineStr">
-        <is>
-          <t>Tooltip flotante para aiDescription en catalog-card</t>
-        </is>
-      </c>
-      <c r="E52" s="6" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
-      <c r="F52" s="7" t="inlineStr">
-        <is>
-          <t>Gerardo Herrera</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="18" customHeight="1">
-      <c r="C53" s="13" t="inlineStr">
-        <is>
-          <t>Corrección</t>
-        </is>
-      </c>
-      <c r="D53" s="9" t="inlineStr">
-        <is>
-          <t>Toast confirm en top, mensaje de confirmacion actualizado</t>
-        </is>
-      </c>
-      <c r="E53" s="10" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
-      <c r="F53" s="11" t="inlineStr">
+      <c r="D53" s="5" t="inlineStr">
+        <is>
+          <t>Toast confirm card para borrado de app en Mis Apps</t>
+        </is>
+      </c>
+      <c r="E53" s="6" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="F53" s="7" t="inlineStr">
         <is>
           <t>Gerardo Herrera</t>
         </is>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
-      <c r="C54" s="8" t="inlineStr">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>Mar</t>
+        </is>
+      </c>
+      <c r="C54" s="13" t="inlineStr">
+        <is>
+          <t>Corrección</t>
+        </is>
+      </c>
+      <c r="D54" s="5" t="inlineStr">
+        <is>
+          <t>corrige spinner de IA en tarjetas y previene doble publicación</t>
+        </is>
+      </c>
+      <c r="E54" s="6" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="F54" s="7" t="inlineStr">
+        <is>
+          <t>Gerardo Herrera</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="18" customHeight="1">
+      <c r="C55" s="12" t="inlineStr">
         <is>
           <t>Nueva función</t>
         </is>
       </c>
-      <c r="D54" s="5" t="inlineStr">
-        <is>
-          <t>Toast confirm card para borrado de app en Mis Apps</t>
-        </is>
-      </c>
-      <c r="E54" s="6" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
-      <c r="F54" s="7" t="inlineStr">
-        <is>
-          <t>Gerardo Herrera</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="18" customHeight="1">
-      <c r="A55" s="3" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="B55" s="3" t="inlineStr">
-        <is>
-          <t>Mar</t>
-        </is>
-      </c>
-      <c r="C55" s="13" t="inlineStr">
-        <is>
-          <t>Corrección</t>
-        </is>
-      </c>
-      <c r="D55" s="5" t="inlineStr">
-        <is>
-          <t>corrige spinner de IA en tarjetas y previene doble publicación</t>
-        </is>
-      </c>
-      <c r="E55" s="6" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
-      <c r="F55" s="7" t="inlineStr">
+      <c r="D55" s="9" t="inlineStr">
+        <is>
+          <t>spinner en tarjeta con polling y actualización automática de IA</t>
+        </is>
+      </c>
+      <c r="E55" s="10" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="F55" s="11" t="inlineStr">
         <is>
           <t>Gerardo Herrera</t>
         </is>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
-      <c r="C56" s="8" t="inlineStr">
-        <is>
-          <t>Nueva función</t>
-        </is>
-      </c>
-      <c r="D56" s="9" t="inlineStr">
-        <is>
-          <t>spinner en tarjeta con polling y actualización automática de IA</t>
-        </is>
-      </c>
-      <c r="E56" s="10" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
-      <c r="F56" s="11" t="inlineStr">
+      <c r="C56" s="15" t="inlineStr">
+        <is>
+          <t>Rendimiento</t>
+        </is>
+      </c>
+      <c r="D56" s="5" t="inlineStr">
+        <is>
+          <t>mueve analyzeHtmlAndUpdate a background en POST y PUT</t>
+        </is>
+      </c>
+      <c r="E56" s="6" t="inlineStr">
+        <is>
+          <t>BACKEND</t>
+        </is>
+      </c>
+      <c r="F56" s="7" t="inlineStr">
         <is>
           <t>Gerardo Herrera</t>
         </is>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
-      <c r="C57" s="15" t="inlineStr">
-        <is>
-          <t>Rendimiento</t>
-        </is>
-      </c>
-      <c r="D57" s="5" t="inlineStr">
-        <is>
-          <t>mueve analyzeHtmlAndUpdate a background en POST y PUT</t>
-        </is>
-      </c>
-      <c r="E57" s="6" t="inlineStr">
-        <is>
-          <t>BACKEND</t>
-        </is>
-      </c>
-      <c r="F57" s="7" t="inlineStr">
+      <c r="C57" s="13" t="inlineStr">
+        <is>
+          <t>Corrección</t>
+        </is>
+      </c>
+      <c r="D57" s="9" t="inlineStr">
+        <is>
+          <t>cierra tooltip al quitar app de favoritos</t>
+        </is>
+      </c>
+      <c r="E57" s="10" t="inlineStr">
+        <is>
+          <t>FAVORITES</t>
+        </is>
+      </c>
+      <c r="F57" s="11" t="inlineStr">
         <is>
           <t>Gerardo Herrera</t>
         </is>
@@ -1891,17 +1891,17 @@
           <t>Corrección</t>
         </is>
       </c>
-      <c r="D58" s="9" t="inlineStr">
-        <is>
-          <t>cierra tooltip al quitar app de favoritos</t>
-        </is>
-      </c>
-      <c r="E58" s="10" t="inlineStr">
-        <is>
-          <t>FAVORITES</t>
-        </is>
-      </c>
-      <c r="F58" s="11" t="inlineStr">
+      <c r="D58" s="5" t="inlineStr">
+        <is>
+          <t>limpia deployProgress al resetear wizard</t>
+        </is>
+      </c>
+      <c r="E58" s="6" t="inlineStr">
+        <is>
+          <t>PUBLISH</t>
+        </is>
+      </c>
+      <c r="F58" s="7" t="inlineStr">
         <is>
           <t>Gerardo Herrera</t>
         </is>
@@ -1913,17 +1913,17 @@
           <t>Corrección</t>
         </is>
       </c>
-      <c r="D59" s="5" t="inlineStr">
-        <is>
-          <t>limpia deployProgress al resetear wizard</t>
-        </is>
-      </c>
-      <c r="E59" s="6" t="inlineStr">
-        <is>
-          <t>PUBLISH</t>
-        </is>
-      </c>
-      <c r="F59" s="7" t="inlineStr">
+      <c r="D59" s="9" t="inlineStr">
+        <is>
+          <t>cambia color de texto en ext-info-box a blanco para mejor legibilidad</t>
+        </is>
+      </c>
+      <c r="E59" s="10" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="F59" s="11" t="inlineStr">
         <is>
           <t>Gerardo Herrera</t>
         </is>
@@ -1935,17 +1935,17 @@
           <t>Corrección</t>
         </is>
       </c>
-      <c r="D60" s="9" t="inlineStr">
-        <is>
-          <t>cambia color de texto en ext-info-box a blanco para mejor legibilidad</t>
-        </is>
-      </c>
-      <c r="E60" s="10" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
-      <c r="F60" s="11" t="inlineStr">
+      <c r="D60" s="5" t="inlineStr">
+        <is>
+          <t>limpia scriptIds obsoletos al renderizar favoritos</t>
+        </is>
+      </c>
+      <c r="E60" s="6" t="inlineStr">
+        <is>
+          <t>FAVORITES</t>
+        </is>
+      </c>
+      <c r="F60" s="7" t="inlineStr">
         <is>
           <t>Gerardo Herrera</t>
         </is>
@@ -1957,17 +1957,17 @@
           <t>Corrección</t>
         </is>
       </c>
-      <c r="D61" s="5" t="inlineStr">
-        <is>
-          <t>limpia scriptIds obsoletos al renderizar favoritos</t>
-        </is>
-      </c>
-      <c r="E61" s="6" t="inlineStr">
+      <c r="D61" s="9" t="inlineStr">
+        <is>
+          <t>limpia app eliminada de catalogData y sl_favs al borrar</t>
+        </is>
+      </c>
+      <c r="E61" s="10" t="inlineStr">
         <is>
           <t>FAVORITES</t>
         </is>
       </c>
-      <c r="F61" s="7" t="inlineStr">
+      <c r="F61" s="11" t="inlineStr">
         <is>
           <t>Gerardo Herrera</t>
         </is>
@@ -1979,23 +1979,33 @@
           <t>Corrección</t>
         </is>
       </c>
-      <c r="D62" s="9" t="inlineStr">
-        <is>
-          <t>limpia app eliminada de catalogData y sl_favs al borrar</t>
-        </is>
-      </c>
-      <c r="E62" s="10" t="inlineStr">
-        <is>
-          <t>FAVORITES</t>
-        </is>
-      </c>
-      <c r="F62" s="11" t="inlineStr">
+      <c r="D62" s="5" t="inlineStr">
+        <is>
+          <t>restringe prompts de iconos a un solo elemento visual</t>
+        </is>
+      </c>
+      <c r="E62" s="6" t="inlineStr">
+        <is>
+          <t>ICONS</t>
+        </is>
+      </c>
+      <c r="F62" s="7" t="inlineStr">
         <is>
           <t>Gerardo Herrera</t>
         </is>
       </c>
     </row>
     <row r="63" ht="18" customHeight="1">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>Mié</t>
+        </is>
+      </c>
       <c r="C63" s="13" t="inlineStr">
         <is>
           <t>Corrección</t>
@@ -2003,12 +2013,12 @@
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>restringe prompts de iconos a un solo elemento visual</t>
+          <t>fondo tenue solo en al-ai-desc (rtp-soft), quita de al-desc</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr">
         <is>
-          <t>ICONS</t>
+          <t>UI</t>
         </is>
       </c>
       <c r="F63" s="7" t="inlineStr">
@@ -2018,76 +2028,66 @@
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
-      <c r="A64" s="3" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="B64" s="3" t="inlineStr">
-        <is>
-          <t>Mié</t>
-        </is>
-      </c>
       <c r="C64" s="13" t="inlineStr">
         <is>
           <t>Corrección</t>
         </is>
       </c>
-      <c r="D64" s="5" t="inlineStr">
-        <is>
-          <t>fondo tenue solo en al-ai-desc (rtp-soft), quita de al-desc</t>
-        </is>
-      </c>
-      <c r="E64" s="6" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
-      <c r="F64" s="7" t="inlineStr">
+      <c r="D64" s="9" t="inlineStr">
+        <is>
+          <t>deja fondo tenue solo en al-desc, quita de al-ai-desc y al-audience</t>
+        </is>
+      </c>
+      <c r="E64" s="10" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="F64" s="11" t="inlineStr">
         <is>
           <t>Gerardo Herrera</t>
         </is>
       </c>
     </row>
     <row r="65" ht="18" customHeight="1">
-      <c r="C65" s="13" t="inlineStr">
-        <is>
-          <t>Corrección</t>
-        </is>
-      </c>
-      <c r="D65" s="9" t="inlineStr">
-        <is>
-          <t>deja fondo tenue solo en al-desc, quita de al-ai-desc y al-audience</t>
-        </is>
-      </c>
-      <c r="E65" s="10" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
-      <c r="F65" s="11" t="inlineStr">
+      <c r="C65" s="12" t="inlineStr">
+        <is>
+          <t>Nueva función</t>
+        </is>
+      </c>
+      <c r="D65" s="5" t="inlineStr">
+        <is>
+          <t>fondo tenue en descripción y audiencia de mis apps publicadas</t>
+        </is>
+      </c>
+      <c r="E65" s="6" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="F65" s="7" t="inlineStr">
         <is>
           <t>Gerardo Herrera</t>
         </is>
       </c>
     </row>
     <row r="66" ht="18" customHeight="1">
-      <c r="C66" s="8" t="inlineStr">
-        <is>
-          <t>Nueva función</t>
-        </is>
-      </c>
-      <c r="D66" s="5" t="inlineStr">
-        <is>
-          <t>fondo tenue en descripción y audiencia de mis apps publicadas</t>
-        </is>
-      </c>
-      <c r="E66" s="6" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
-      <c r="F66" s="7" t="inlineStr">
+      <c r="C66" s="13" t="inlineStr">
+        <is>
+          <t>Corrección</t>
+        </is>
+      </c>
+      <c r="D66" s="9" t="inlineStr">
+        <is>
+          <t>usa iconSrc() para URL del icono en mis apps publicadas</t>
+        </is>
+      </c>
+      <c r="E66" s="10" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="F66" s="11" t="inlineStr">
         <is>
           <t>Gerardo Herrera</t>
         </is>
@@ -2099,61 +2099,71 @@
           <t>Corrección</t>
         </is>
       </c>
-      <c r="D67" s="9" t="inlineStr">
-        <is>
-          <t>usa iconSrc() para URL del icono en mis apps publicadas</t>
-        </is>
-      </c>
-      <c r="E67" s="10" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
-      <c r="F67" s="11" t="inlineStr">
+      <c r="D67" s="5" t="inlineStr">
+        <is>
+          <t>muestra icono real en mis apps publicadas desde polling de IA</t>
+        </is>
+      </c>
+      <c r="E67" s="6" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="F67" s="7" t="inlineStr">
         <is>
           <t>Gerardo Herrera</t>
         </is>
       </c>
     </row>
     <row r="68" ht="18" customHeight="1">
-      <c r="C68" s="13" t="inlineStr">
-        <is>
-          <t>Corrección</t>
-        </is>
-      </c>
-      <c r="D68" s="5" t="inlineStr">
-        <is>
-          <t>muestra icono real en mis apps publicadas desde polling de IA</t>
-        </is>
-      </c>
-      <c r="E68" s="6" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
-      <c r="F68" s="7" t="inlineStr">
+      <c r="C68" s="12" t="inlineStr">
+        <is>
+          <t>Nueva función</t>
+        </is>
+      </c>
+      <c r="D68" s="9" t="inlineStr">
+        <is>
+          <t>agrega icono de app en la sección de mis apps publicadas</t>
+        </is>
+      </c>
+      <c r="E68" s="10" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="F68" s="11" t="inlineStr">
         <is>
           <t>Gerardo Herrera</t>
         </is>
       </c>
     </row>
     <row r="69" ht="18" customHeight="1">
-      <c r="C69" s="8" t="inlineStr">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>Jue</t>
+        </is>
+      </c>
+      <c r="C69" s="12" t="inlineStr">
         <is>
           <t>Nueva función</t>
         </is>
       </c>
-      <c r="D69" s="9" t="inlineStr">
-        <is>
-          <t>agrega icono de app en la sección de mis apps publicadas</t>
-        </is>
-      </c>
-      <c r="E69" s="10" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
-      <c r="F69" s="11" t="inlineStr">
+      <c r="D69" s="5" t="inlineStr">
+        <is>
+          <t>estadisticas de uso por app para owner y admin</t>
+        </is>
+      </c>
+      <c r="E69" s="6" t="inlineStr">
+        <is>
+          <t>ANALYTICS</t>
+        </is>
+      </c>
+      <c r="F69" s="7" t="inlineStr">
         <is>
           <t>Gerardo Herrera</t>
         </is>
@@ -2162,27 +2172,27 @@
     <row r="70" ht="18" customHeight="1">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>Jue</t>
-        </is>
-      </c>
-      <c r="C70" s="8" t="inlineStr">
-        <is>
-          <t>Nueva función</t>
+          <t>Vie</t>
+        </is>
+      </c>
+      <c r="C70" s="13" t="inlineStr">
+        <is>
+          <t>Corrección</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>estadisticas de uso por app para owner y admin</t>
+          <t>reordena EXTERNAL_CONTACTS_AUTHORIZED</t>
         </is>
       </c>
       <c r="E70" s="6" t="inlineStr">
         <is>
-          <t>ANALYTICS</t>
+          <t>AUTH</t>
         </is>
       </c>
       <c r="F70" s="7" t="inlineStr">
@@ -2194,27 +2204,27 @@
     <row r="71" ht="18" customHeight="1">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>Vie</t>
-        </is>
-      </c>
-      <c r="C71" s="13" t="inlineStr">
-        <is>
-          <t>Corrección</t>
+          <t>Lun</t>
+        </is>
+      </c>
+      <c r="C71" s="12" t="inlineStr">
+        <is>
+          <t>Nueva función</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>reordena EXTERNAL_CONTACTS_AUTHORIZED</t>
+          <t>agrega ICONS_PATH_PREFIX para configurar prefijo de ruta en bucket</t>
         </is>
       </c>
       <c r="E71" s="6" t="inlineStr">
         <is>
-          <t>AUTH</t>
+          <t>ICONS</t>
         </is>
       </c>
       <c r="F71" s="7" t="inlineStr">
@@ -2224,98 +2234,88 @@
       </c>
     </row>
     <row r="72" ht="18" customHeight="1">
-      <c r="A72" s="3" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="B72" s="3" t="inlineStr">
-        <is>
-          <t>Lun</t>
-        </is>
-      </c>
-      <c r="C72" s="8" t="inlineStr">
-        <is>
-          <t>Nueva función</t>
-        </is>
-      </c>
-      <c r="D72" s="5" t="inlineStr">
-        <is>
-          <t>agrega ICONS_PATH_PREFIX para configurar prefijo de ruta en bucket</t>
-        </is>
-      </c>
-      <c r="E72" s="6" t="inlineStr">
+      <c r="C72" s="13" t="inlineStr">
+        <is>
+          <t>Corrección</t>
+        </is>
+      </c>
+      <c r="D72" s="9" t="inlineStr">
+        <is>
+          <t>ajusta URLs de CDN de iconos para staging (/dev) y prod</t>
+        </is>
+      </c>
+      <c r="E72" s="10" t="inlineStr">
         <is>
           <t>ICONS</t>
         </is>
       </c>
-      <c r="F72" s="7" t="inlineStr">
+      <c r="F72" s="11" t="inlineStr">
         <is>
           <t>Gerardo Herrera</t>
         </is>
       </c>
     </row>
     <row r="73" ht="18" customHeight="1">
-      <c r="C73" s="13" t="inlineStr">
-        <is>
-          <t>Corrección</t>
-        </is>
-      </c>
-      <c r="D73" s="9" t="inlineStr">
-        <is>
-          <t>ajusta URLs de CDN de iconos para staging (/dev) y prod</t>
-        </is>
-      </c>
-      <c r="E73" s="10" t="inlineStr">
+      <c r="C73" s="8" t="inlineStr">
+        <is>
+          <t>Mantenimiento</t>
+        </is>
+      </c>
+      <c r="D73" s="5" t="inlineStr">
+        <is>
+          <t>Se actualiza lista de correos externos</t>
+        </is>
+      </c>
+      <c r="E73" s="6" t="inlineStr">
+        <is>
+          <t>EXTERNAL_EMAIL</t>
+        </is>
+      </c>
+      <c r="F73" s="7" t="inlineStr">
+        <is>
+          <t>Gerardo Herrera</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="18" customHeight="1">
+      <c r="C74" s="4" t="inlineStr">
+        <is>
+          <t>Documentación</t>
+        </is>
+      </c>
+      <c r="D74" s="9" t="inlineStr">
+        <is>
+          <t>actualiza documentacion a v1.5 (iconos IA, analytics, externos, share, favoritos)</t>
+        </is>
+      </c>
+      <c r="E74" s="10" t="inlineStr">
+        <is>
+          <t>ICONOS IA, ANALYTICS, EXTERNOS, SHARE, FAVORITOS</t>
+        </is>
+      </c>
+      <c r="F74" s="11" t="inlineStr">
+        <is>
+          <t>Gerardo Herrera</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="18" customHeight="1">
+      <c r="C75" s="13" t="inlineStr">
+        <is>
+          <t>Corrección</t>
+        </is>
+      </c>
+      <c r="D75" s="5" t="inlineStr">
+        <is>
+          <t>quita borde blanco grueso del prompt de generación de íconos</t>
+        </is>
+      </c>
+      <c r="E75" s="6" t="inlineStr">
         <is>
           <t>ICONS</t>
         </is>
       </c>
-      <c r="F73" s="11" t="inlineStr">
-        <is>
-          <t>Gerardo Herrera</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="18" customHeight="1">
-      <c r="C74" s="12" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
-        </is>
-      </c>
-      <c r="D74" s="5" t="inlineStr">
-        <is>
-          <t>Se actualiza lista de correos externos</t>
-        </is>
-      </c>
-      <c r="E74" s="6" t="inlineStr">
-        <is>
-          <t>EXTERNAL_EMAIL</t>
-        </is>
-      </c>
-      <c r="F74" s="7" t="inlineStr">
-        <is>
-          <t>Gerardo Herrera</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="18" customHeight="1">
-      <c r="C75" s="4" t="inlineStr">
-        <is>
-          <t>Documentación</t>
-        </is>
-      </c>
-      <c r="D75" s="9" t="inlineStr">
-        <is>
-          <t>actualiza documentacion a v1.5 (iconos IA, analytics, externos, share, favoritos)</t>
-        </is>
-      </c>
-      <c r="E75" s="10" t="inlineStr">
-        <is>
-          <t>ICONOS IA, ANALYTICS, EXTERNOS, SHARE, FAVORITOS</t>
-        </is>
-      </c>
-      <c r="F75" s="11" t="inlineStr">
+      <c r="F75" s="7" t="inlineStr">
         <is>
           <t>Gerardo Herrera</t>
         </is>
@@ -2327,71 +2327,71 @@
           <t>Corrección</t>
         </is>
       </c>
-      <c r="D76" s="5" t="inlineStr">
-        <is>
-          <t>quita borde blanco grueso del prompt de generación de íconos</t>
-        </is>
-      </c>
-      <c r="E76" s="6" t="inlineStr">
+      <c r="D76" s="9" t="inlineStr">
+        <is>
+          <t>cambia estilo de íconos de sticker a flat en prompt de Gemini</t>
+        </is>
+      </c>
+      <c r="E76" s="10" t="inlineStr">
         <is>
           <t>ICONS</t>
         </is>
       </c>
-      <c r="F76" s="7" t="inlineStr">
+      <c r="F76" s="11" t="inlineStr">
         <is>
           <t>Gerardo Herrera</t>
         </is>
       </c>
     </row>
     <row r="77" ht="18" customHeight="1">
+      <c r="A77" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="inlineStr">
+        <is>
+          <t>Mar</t>
+        </is>
+      </c>
       <c r="C77" s="13" t="inlineStr">
         <is>
           <t>Corrección</t>
         </is>
       </c>
-      <c r="D77" s="9" t="inlineStr">
-        <is>
-          <t>cambia estilo de íconos de sticker a flat en prompt de Gemini</t>
-        </is>
-      </c>
-      <c r="E77" s="10" t="inlineStr">
-        <is>
-          <t>ICONS</t>
-        </is>
-      </c>
-      <c r="F77" s="11" t="inlineStr">
+      <c r="D77" s="5" t="inlineStr">
+        <is>
+          <t>trunca descripción a 55 chars + … en tarjetas sp-app del spotlight</t>
+        </is>
+      </c>
+      <c r="E77" s="6" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="F77" s="7" t="inlineStr">
         <is>
           <t>Gerardo Herrera</t>
         </is>
       </c>
     </row>
     <row r="78" ht="18" customHeight="1">
-      <c r="A78" s="3" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="B78" s="3" t="inlineStr">
-        <is>
-          <t>Mar</t>
-        </is>
-      </c>
       <c r="C78" s="13" t="inlineStr">
         <is>
           <t>Corrección</t>
         </is>
       </c>
-      <c r="D78" s="5" t="inlineStr">
-        <is>
-          <t>trunca descripción a 55 chars + … en tarjetas sp-app del spotlight</t>
-        </is>
-      </c>
-      <c r="E78" s="6" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
-      <c r="F78" s="7" t="inlineStr">
+      <c r="D78" s="9" t="inlineStr">
+        <is>
+          <t>reemplaza descripción por categoría en tarjetas sp-app del spotlight</t>
+        </is>
+      </c>
+      <c r="E78" s="10" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="F78" s="11" t="inlineStr">
         <is>
           <t>Gerardo Herrera</t>
         </is>
@@ -2403,78 +2403,88 @@
           <t>Corrección</t>
         </is>
       </c>
-      <c r="D79" s="9" t="inlineStr">
-        <is>
-          <t>reemplaza descripción por categoría en tarjetas sp-app del spotlight</t>
-        </is>
-      </c>
-      <c r="E79" s="10" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
-      <c r="F79" s="11" t="inlineStr">
+      <c r="D79" s="5" t="inlineStr">
+        <is>
+          <t>corrige desajuste de descripción en spotlight</t>
+        </is>
+      </c>
+      <c r="E79" s="6" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="F79" s="7" t="inlineStr">
         <is>
           <t>Gerardo Herrera</t>
         </is>
       </c>
     </row>
     <row r="80" ht="18" customHeight="1">
-      <c r="C80" s="13" t="inlineStr">
-        <is>
-          <t>Corrección</t>
-        </is>
-      </c>
-      <c r="D80" s="5" t="inlineStr">
-        <is>
-          <t>corrige desajuste de descripción en spotlight</t>
-        </is>
-      </c>
-      <c r="E80" s="6" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
-      <c r="F80" s="7" t="inlineStr">
+      <c r="C80" s="8" t="inlineStr">
+        <is>
+          <t>Mantenimiento</t>
+        </is>
+      </c>
+      <c r="D80" s="9" t="inlineStr">
+        <is>
+          <t>actualiza versión de TinaCode a v1.4</t>
+        </is>
+      </c>
+      <c r="E80" s="10" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="F80" s="11" t="inlineStr">
         <is>
           <t>Gerardo Herrera</t>
         </is>
       </c>
     </row>
     <row r="81" ht="18" customHeight="1">
-      <c r="C81" s="12" t="inlineStr">
+      <c r="C81" s="8" t="inlineStr">
         <is>
           <t>Mantenimiento</t>
         </is>
       </c>
-      <c r="D81" s="9" t="inlineStr">
-        <is>
-          <t>actualiza versión de TinaCode a v1.4</t>
-        </is>
-      </c>
-      <c r="E81" s="10" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
-      <c r="F81" s="11" t="inlineStr">
+      <c r="D81" s="5" t="inlineStr">
+        <is>
+          <t>agrega apliego a externos autorizados y script de backfill AI</t>
+        </is>
+      </c>
+      <c r="E81" s="6" t="inlineStr"/>
+      <c r="F81" s="7" t="inlineStr">
         <is>
           <t>Gerardo Herrera</t>
         </is>
       </c>
     </row>
     <row r="82" ht="18" customHeight="1">
-      <c r="C82" s="12" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
+      <c r="A82" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>Mié</t>
+        </is>
+      </c>
+      <c r="C82" s="13" t="inlineStr">
+        <is>
+          <t>Corrección</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>agrega apliego a externos autorizados y script de backfill AI</t>
-        </is>
-      </c>
-      <c r="E82" s="6" t="inlineStr"/>
+          <t>consolida escala tipográfica — elimina valores fraccionados</t>
+        </is>
+      </c>
+      <c r="E82" s="6" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
       <c r="F82" s="7" t="inlineStr">
         <is>
           <t>Gerardo Herrera</t>
@@ -2482,86 +2492,76 @@
       </c>
     </row>
     <row r="83" ht="18" customHeight="1">
-      <c r="A83" s="3" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="B83" s="3" t="inlineStr">
-        <is>
-          <t>Mié</t>
-        </is>
-      </c>
       <c r="C83" s="13" t="inlineStr">
         <is>
           <t>Corrección</t>
         </is>
       </c>
-      <c r="D83" s="5" t="inlineStr">
-        <is>
-          <t>consolida escala tipográfica — elimina valores fraccionados</t>
-        </is>
-      </c>
-      <c r="E83" s="6" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
-      <c r="F83" s="7" t="inlineStr">
+      <c r="D83" s="9" t="inlineStr">
+        <is>
+          <t>cambia sp-apps a 1 columna en spotlight</t>
+        </is>
+      </c>
+      <c r="E83" s="10" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="F83" s="11" t="inlineStr">
         <is>
           <t>Gerardo Herrera</t>
         </is>
       </c>
     </row>
     <row r="84" ht="18" customHeight="1">
-      <c r="C84" s="13" t="inlineStr">
-        <is>
-          <t>Corrección</t>
-        </is>
-      </c>
-      <c r="D84" s="9" t="inlineStr">
-        <is>
-          <t>cambia sp-apps a 1 columna en spotlight</t>
-        </is>
-      </c>
-      <c r="E84" s="10" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
-      <c r="F84" s="11" t="inlineStr">
+      <c r="A84" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B84" s="3" t="inlineStr">
+        <is>
+          <t>Jue</t>
+        </is>
+      </c>
+      <c r="C84" s="12" t="inlineStr">
+        <is>
+          <t>Nueva función</t>
+        </is>
+      </c>
+      <c r="D84" s="5" t="inlineStr">
+        <is>
+          <t>redistribuye cc-row — elimina cc-icon, nuevo cc-bottom con chip + botón</t>
+        </is>
+      </c>
+      <c r="E84" s="6" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="F84" s="7" t="inlineStr">
         <is>
           <t>Gerardo Herrera</t>
         </is>
       </c>
     </row>
     <row r="85" ht="18" customHeight="1">
-      <c r="A85" s="3" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="B85" s="3" t="inlineStr">
-        <is>
-          <t>Jue</t>
-        </is>
-      </c>
-      <c r="C85" s="8" t="inlineStr">
-        <is>
-          <t>Nueva función</t>
-        </is>
-      </c>
-      <c r="D85" s="5" t="inlineStr">
-        <is>
-          <t>redistribuye cc-row — elimina cc-icon, nuevo cc-bottom con chip + botón</t>
-        </is>
-      </c>
-      <c r="E85" s="6" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
-      <c r="F85" s="7" t="inlineStr">
+      <c r="C85" s="13" t="inlineStr">
+        <is>
+          <t>Corrección</t>
+        </is>
+      </c>
+      <c r="D85" s="9" t="inlineStr">
+        <is>
+          <t>ajusta pv-icon a translateY(10px)</t>
+        </is>
+      </c>
+      <c r="E85" s="10" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="F85" s="11" t="inlineStr">
         <is>
           <t>Gerardo Herrera</t>
         </is>
@@ -2573,17 +2573,17 @@
           <t>Corrección</t>
         </is>
       </c>
-      <c r="D86" s="9" t="inlineStr">
-        <is>
-          <t>ajusta pv-icon a translateY(10px)</t>
-        </is>
-      </c>
-      <c r="E86" s="10" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
-      <c r="F86" s="11" t="inlineStr">
+      <c r="D86" s="5" t="inlineStr">
+        <is>
+          <t>baja pv-icon 5px con translateY</t>
+        </is>
+      </c>
+      <c r="E86" s="6" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="F86" s="7" t="inlineStr">
         <is>
           <t>Gerardo Herrera</t>
         </is>
@@ -2595,39 +2595,39 @@
           <t>Corrección</t>
         </is>
       </c>
-      <c r="D87" s="5" t="inlineStr">
-        <is>
-          <t>baja pv-icon 5px con translateY</t>
-        </is>
-      </c>
-      <c r="E87" s="6" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
-      <c r="F87" s="7" t="inlineStr">
+      <c r="D87" s="9" t="inlineStr">
+        <is>
+          <t>regresa pv-icon al centro y reduce cc-preview a 125px</t>
+        </is>
+      </c>
+      <c r="E87" s="10" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="F87" s="11" t="inlineStr">
         <is>
           <t>Gerardo Herrera</t>
         </is>
       </c>
     </row>
     <row r="88" ht="18" customHeight="1">
-      <c r="C88" s="13" t="inlineStr">
-        <is>
-          <t>Corrección</t>
-        </is>
-      </c>
-      <c r="D88" s="9" t="inlineStr">
-        <is>
-          <t>regresa pv-icon al centro y reduce cc-preview a 125px</t>
-        </is>
-      </c>
-      <c r="E88" s="10" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
-      <c r="F88" s="11" t="inlineStr">
+      <c r="C88" s="12" t="inlineStr">
+        <is>
+          <t>Nueva función</t>
+        </is>
+      </c>
+      <c r="D88" s="5" t="inlineStr">
+        <is>
+          <t>redistribuye elementos de cc-preview en catalog-card</t>
+        </is>
+      </c>
+      <c r="E88" s="6" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="F88" s="7" t="inlineStr">
         <is>
           <t>Gerardo Herrera</t>
         </is>
@@ -2636,42 +2636,42 @@
     <row r="89" ht="18" customHeight="1">
       <c r="C89" s="8" t="inlineStr">
         <is>
-          <t>Nueva función</t>
-        </is>
-      </c>
-      <c r="D89" s="5" t="inlineStr">
-        <is>
-          <t>redistribuye elementos de cc-preview en catalog-card</t>
-        </is>
-      </c>
-      <c r="E89" s="6" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
-      <c r="F89" s="7" t="inlineStr">
+          <t>Mantenimiento</t>
+        </is>
+      </c>
+      <c r="D89" s="9" t="inlineStr">
+        <is>
+          <t>acepta REPO y OUT como argumentos CLI en generate_report.py</t>
+        </is>
+      </c>
+      <c r="E89" s="10" t="inlineStr">
+        <is>
+          <t>REPORTS</t>
+        </is>
+      </c>
+      <c r="F89" s="11" t="inlineStr">
         <is>
           <t>Gerardo Herrera</t>
         </is>
       </c>
     </row>
     <row r="90" ht="18" customHeight="1">
-      <c r="C90" s="12" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
-        </is>
-      </c>
-      <c r="D90" s="9" t="inlineStr">
-        <is>
-          <t>acepta REPO y OUT como argumentos CLI en generate_report.py</t>
-        </is>
-      </c>
-      <c r="E90" s="10" t="inlineStr">
-        <is>
-          <t>REPORTS</t>
-        </is>
-      </c>
-      <c r="F90" s="11" t="inlineStr">
+      <c r="C90" s="13" t="inlineStr">
+        <is>
+          <t>Corrección</t>
+        </is>
+      </c>
+      <c r="D90" s="5" t="inlineStr">
+        <is>
+          <t>extrae 13 estilos tipográficos inline a clases CSS</t>
+        </is>
+      </c>
+      <c r="E90" s="6" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="F90" s="7" t="inlineStr">
         <is>
           <t>Gerardo Herrera</t>
         </is>
@@ -2683,17 +2683,17 @@
           <t>Corrección</t>
         </is>
       </c>
-      <c r="D91" s="5" t="inlineStr">
-        <is>
-          <t>extrae 13 estilos tipográficos inline a clases CSS</t>
-        </is>
-      </c>
-      <c r="E91" s="6" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
-      <c r="F91" s="7" t="inlineStr">
+      <c r="D91" s="9" t="inlineStr">
+        <is>
+          <t>agrega line-height explícito a 4 elementos de texto multilinea</t>
+        </is>
+      </c>
+      <c r="E91" s="10" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="F91" s="11" t="inlineStr">
         <is>
           <t>Gerardo Herrera</t>
         </is>
@@ -2705,17 +2705,17 @@
           <t>Corrección</t>
         </is>
       </c>
-      <c r="D92" s="9" t="inlineStr">
-        <is>
-          <t>agrega line-height explícito a 4 elementos de texto multilinea</t>
-        </is>
-      </c>
-      <c r="E92" s="10" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
-      <c r="F92" s="11" t="inlineStr">
+      <c r="D92" s="5" t="inlineStr">
+        <is>
+          <t>agrega font-family a .cat-explore-head .row-eyebrow</t>
+        </is>
+      </c>
+      <c r="E92" s="6" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="F92" s="7" t="inlineStr">
         <is>
           <t>Gerardo Herrera</t>
         </is>
@@ -2727,17 +2727,17 @@
           <t>Corrección</t>
         </is>
       </c>
-      <c r="D93" s="5" t="inlineStr">
-        <is>
-          <t>agrega font-family a .cat-explore-head .row-eyebrow</t>
-        </is>
-      </c>
-      <c r="E93" s="6" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
-      <c r="F93" s="7" t="inlineStr">
+      <c r="D93" s="9" t="inlineStr">
+        <is>
+          <t>sube font-size de labels del gráfico analytics de 9px a 11px</t>
+        </is>
+      </c>
+      <c r="E93" s="10" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="F93" s="11" t="inlineStr">
         <is>
           <t>Gerardo Herrera</t>
         </is>
@@ -2749,17 +2749,17 @@
           <t>Corrección</t>
         </is>
       </c>
-      <c r="D94" s="9" t="inlineStr">
-        <is>
-          <t>sube font-size de labels del gráfico analytics de 9px a 11px</t>
-        </is>
-      </c>
-      <c r="E94" s="10" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
-      <c r="F94" s="11" t="inlineStr">
+      <c r="D94" s="5" t="inlineStr">
+        <is>
+          <t>corrige letter-spacing de .login-card h1 a -.02em</t>
+        </is>
+      </c>
+      <c r="E94" s="6" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="F94" s="7" t="inlineStr">
         <is>
           <t>Gerardo Herrera</t>
         </is>
@@ -2771,17 +2771,17 @@
           <t>Corrección</t>
         </is>
       </c>
-      <c r="D95" s="5" t="inlineStr">
-        <is>
-          <t>corrige letter-spacing de .login-card h1 a -.02em</t>
-        </is>
-      </c>
-      <c r="E95" s="6" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
-      <c r="F95" s="7" t="inlineStr">
+      <c r="D95" s="9" t="inlineStr">
+        <is>
+          <t>convierte letter-spacing de px a em en toda la hoja de estilos</t>
+        </is>
+      </c>
+      <c r="E95" s="10" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="F95" s="11" t="inlineStr">
         <is>
           <t>Gerardo Herrera</t>
         </is>
@@ -2793,69 +2793,45 @@
           <t>Corrección</t>
         </is>
       </c>
-      <c r="D96" s="9" t="inlineStr">
-        <is>
-          <t>convierte letter-spacing de px a em en toda la hoja de estilos</t>
-        </is>
-      </c>
-      <c r="E96" s="10" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
-      <c r="F96" s="11" t="inlineStr">
-        <is>
-          <t>Gerardo Herrera</t>
-        </is>
-      </c>
-    </row>
-    <row r="97" ht="18" customHeight="1">
-      <c r="C97" s="13" t="inlineStr">
-        <is>
-          <t>Corrección</t>
-        </is>
-      </c>
-      <c r="D97" s="5" t="inlineStr">
+      <c r="D96" s="5" t="inlineStr">
         <is>
           <t>elimina definiciones CSS conflictivas — unifica escala tipográfica</t>
         </is>
       </c>
-      <c r="E97" s="6" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
-      <c r="F97" s="7" t="inlineStr">
+      <c r="E96" s="6" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="F96" s="7" t="inlineStr">
         <is>
           <t>Gerardo Herrera</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="23">
-    <mergeCell ref="A9:A23"/>
-    <mergeCell ref="B78:B82"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="A64:A69"/>
-    <mergeCell ref="A55:A63"/>
-    <mergeCell ref="B72:B77"/>
-    <mergeCell ref="A34:A54"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="A24:A33"/>
-    <mergeCell ref="A85:A97"/>
-    <mergeCell ref="B83:B84"/>
-    <mergeCell ref="B9:B23"/>
-    <mergeCell ref="B55:B63"/>
-    <mergeCell ref="A5:A8"/>
-    <mergeCell ref="B85:B97"/>
-    <mergeCell ref="B5:B8"/>
-    <mergeCell ref="A78:A82"/>
-    <mergeCell ref="B64:B69"/>
+  <mergeCells count="21">
+    <mergeCell ref="B33:B53"/>
+    <mergeCell ref="B8:B22"/>
+    <mergeCell ref="B82:B83"/>
+    <mergeCell ref="A84:A96"/>
+    <mergeCell ref="B71:B76"/>
+    <mergeCell ref="A77:A81"/>
+    <mergeCell ref="B84:B96"/>
+    <mergeCell ref="A71:A76"/>
+    <mergeCell ref="A23:A32"/>
+    <mergeCell ref="B23:B32"/>
+    <mergeCell ref="B54:B62"/>
+    <mergeCell ref="A8:A22"/>
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="B77:B81"/>
+    <mergeCell ref="B4:B7"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="B34:B54"/>
-    <mergeCell ref="A83:A84"/>
-    <mergeCell ref="A72:A77"/>
-    <mergeCell ref="B24:B33"/>
+    <mergeCell ref="A63:A68"/>
+    <mergeCell ref="A33:A53"/>
+    <mergeCell ref="A82:A83"/>
+    <mergeCell ref="A54:A62"/>
+    <mergeCell ref="B63:B68"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2900,7 +2876,7 @@
       </c>
       <c r="C3" s="20" t="inlineStr">
         <is>
-          <t>59%</t>
+          <t>60%</t>
         </is>
       </c>
     </row>
@@ -2911,7 +2887,7 @@
         </is>
       </c>
       <c r="B4" s="19" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C4" s="20" t="inlineStr">
         <is>
@@ -2986,7 +2962,7 @@
         </is>
       </c>
       <c r="B10" s="19" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="11">
@@ -3023,7 +2999,7 @@
         </is>
       </c>
       <c r="B15" s="19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/cambios_tinacode.xlsx
+++ b/cambios_tinacode.xlsx
@@ -581,7 +581,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F97"/>
+  <dimension ref="A1:F100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -595,7 +595,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Reporte de Cambios · TinaCode  —  2026-06-01 al 2026-06-19</t>
+          <t>Reporte de Cambios · TinaCode  —  2026-06-01 al 2026-06-20</t>
         </is>
       </c>
     </row>
@@ -664,6 +664,16 @@
       </c>
     </row>
     <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Lun</t>
+        </is>
+      </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
           <t>Nueva función</t>
@@ -714,6 +724,16 @@
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Mié</t>
+        </is>
+      </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
           <t>Mantenimiento</t>
@@ -732,6 +752,16 @@
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Mié</t>
+        </is>
+      </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
           <t>Mantenimiento</t>
@@ -750,6 +780,16 @@
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Mié</t>
+        </is>
+      </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
           <t>Mantenimiento</t>
@@ -800,6 +840,16 @@
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Jue</t>
+        </is>
+      </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
           <t>Nueva función</t>
@@ -822,6 +872,16 @@
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Jue</t>
+        </is>
+      </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
           <t>Nueva función</t>
@@ -844,6 +904,16 @@
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Jue</t>
+        </is>
+      </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
           <t>Mantenimiento</t>
@@ -866,6 +936,16 @@
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Jue</t>
+        </is>
+      </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
           <t>Mantenimiento</t>
@@ -888,6 +968,16 @@
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Jue</t>
+        </is>
+      </c>
       <c r="C14" s="13" t="inlineStr">
         <is>
           <t>Corrección</t>
@@ -910,6 +1000,16 @@
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Jue</t>
+        </is>
+      </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
           <t>Nueva función</t>
@@ -932,6 +1032,16 @@
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Jue</t>
+        </is>
+      </c>
       <c r="C16" s="13" t="inlineStr">
         <is>
           <t>Corrección</t>
@@ -954,6 +1064,16 @@
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Jue</t>
+        </is>
+      </c>
       <c r="C17" s="13" t="inlineStr">
         <is>
           <t>Corrección</t>
@@ -976,6 +1096,16 @@
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Jue</t>
+        </is>
+      </c>
       <c r="C18" s="13" t="inlineStr">
         <is>
           <t>Corrección</t>
@@ -998,6 +1128,16 @@
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Jue</t>
+        </is>
+      </c>
       <c r="C19" s="13" t="inlineStr">
         <is>
           <t>Corrección</t>
@@ -1020,6 +1160,16 @@
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Jue</t>
+        </is>
+      </c>
       <c r="C20" s="13" t="inlineStr">
         <is>
           <t>Corrección</t>
@@ -1042,6 +1192,16 @@
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>Jue</t>
+        </is>
+      </c>
       <c r="C21" s="13" t="inlineStr">
         <is>
           <t>Corrección</t>
@@ -1064,6 +1224,16 @@
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Jue</t>
+        </is>
+      </c>
       <c r="C22" s="13" t="inlineStr">
         <is>
           <t>Corrección</t>
@@ -1086,6 +1256,16 @@
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>Jue</t>
+        </is>
+      </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
           <t>Nueva función</t>
@@ -1140,6 +1320,16 @@
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Vie</t>
+        </is>
+      </c>
       <c r="C25" s="13" t="inlineStr">
         <is>
           <t>Corrección</t>
@@ -1162,6 +1352,16 @@
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Vie</t>
+        </is>
+      </c>
       <c r="C26" s="13" t="inlineStr">
         <is>
           <t>Corrección</t>
@@ -1184,6 +1384,16 @@
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>Vie</t>
+        </is>
+      </c>
       <c r="C27" s="13" t="inlineStr">
         <is>
           <t>Corrección</t>
@@ -1206,6 +1416,16 @@
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Vie</t>
+        </is>
+      </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
           <t>Nueva función</t>
@@ -1228,6 +1448,16 @@
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>Vie</t>
+        </is>
+      </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
           <t>Nueva función</t>
@@ -1250,6 +1480,16 @@
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>Vie</t>
+        </is>
+      </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
           <t>Nueva función</t>
@@ -1272,6 +1512,16 @@
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>Vie</t>
+        </is>
+      </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
           <t>Nueva función</t>
@@ -1294,6 +1544,16 @@
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>Vie</t>
+        </is>
+      </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
           <t>Nueva función</t>
@@ -1316,6 +1576,16 @@
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>Vie</t>
+        </is>
+      </c>
       <c r="C33" s="13" t="inlineStr">
         <is>
           <t>Corrección</t>
@@ -1370,6 +1640,16 @@
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>Lun</t>
+        </is>
+      </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
           <t>Nueva función</t>
@@ -1392,6 +1672,16 @@
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>Lun</t>
+        </is>
+      </c>
       <c r="C36" s="13" t="inlineStr">
         <is>
           <t>Corrección</t>
@@ -1414,6 +1704,16 @@
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>Lun</t>
+        </is>
+      </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
           <t>Nueva función</t>
@@ -1436,6 +1736,16 @@
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>Lun</t>
+        </is>
+      </c>
       <c r="C38" s="13" t="inlineStr">
         <is>
           <t>Corrección</t>
@@ -1458,6 +1768,16 @@
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>Lun</t>
+        </is>
+      </c>
       <c r="C39" s="13" t="inlineStr">
         <is>
           <t>Corrección</t>
@@ -1480,6 +1800,16 @@
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>Lun</t>
+        </is>
+      </c>
       <c r="C40" s="13" t="inlineStr">
         <is>
           <t>Corrección</t>
@@ -1502,6 +1832,16 @@
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>Lun</t>
+        </is>
+      </c>
       <c r="C41" s="13" t="inlineStr">
         <is>
           <t>Corrección</t>
@@ -1524,6 +1864,16 @@
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>Lun</t>
+        </is>
+      </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
           <t>Nueva función</t>
@@ -1546,6 +1896,16 @@
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>Lun</t>
+        </is>
+      </c>
       <c r="C43" s="13" t="inlineStr">
         <is>
           <t>Corrección</t>
@@ -1568,6 +1928,16 @@
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>Lun</t>
+        </is>
+      </c>
       <c r="C44" s="13" t="inlineStr">
         <is>
           <t>Corrección</t>
@@ -1590,6 +1960,16 @@
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>Lun</t>
+        </is>
+      </c>
       <c r="C45" s="13" t="inlineStr">
         <is>
           <t>Corrección</t>
@@ -1612,6 +1992,16 @@
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>Lun</t>
+        </is>
+      </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
           <t>Nueva función</t>
@@ -1634,6 +2024,16 @@
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>Lun</t>
+        </is>
+      </c>
       <c r="C47" s="13" t="inlineStr">
         <is>
           <t>Corrección</t>
@@ -1656,6 +2056,16 @@
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>Lun</t>
+        </is>
+      </c>
       <c r="C48" s="14" t="inlineStr">
         <is>
           <t>Refactorización</t>
@@ -1678,6 +2088,16 @@
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>Lun</t>
+        </is>
+      </c>
       <c r="C49" s="8" t="inlineStr">
         <is>
           <t>Nueva función</t>
@@ -1700,6 +2120,16 @@
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>Lun</t>
+        </is>
+      </c>
       <c r="C50" s="13" t="inlineStr">
         <is>
           <t>Corrección</t>
@@ -1722,6 +2152,16 @@
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>Lun</t>
+        </is>
+      </c>
       <c r="C51" s="13" t="inlineStr">
         <is>
           <t>Corrección</t>
@@ -1744,6 +2184,16 @@
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>Lun</t>
+        </is>
+      </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
           <t>Nueva función</t>
@@ -1766,6 +2216,16 @@
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>Lun</t>
+        </is>
+      </c>
       <c r="C53" s="13" t="inlineStr">
         <is>
           <t>Corrección</t>
@@ -1788,6 +2248,16 @@
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>Lun</t>
+        </is>
+      </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
           <t>Nueva función</t>
@@ -1842,6 +2312,16 @@
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>Mar</t>
+        </is>
+      </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
           <t>Nueva función</t>
@@ -1864,6 +2344,16 @@
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>Mar</t>
+        </is>
+      </c>
       <c r="C57" s="15" t="inlineStr">
         <is>
           <t>Rendimiento</t>
@@ -1886,6 +2376,16 @@
       </c>
     </row>
     <row r="58" ht="18" customHeight="1">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>Mar</t>
+        </is>
+      </c>
       <c r="C58" s="13" t="inlineStr">
         <is>
           <t>Corrección</t>
@@ -1908,6 +2408,16 @@
       </c>
     </row>
     <row r="59" ht="18" customHeight="1">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>Mar</t>
+        </is>
+      </c>
       <c r="C59" s="13" t="inlineStr">
         <is>
           <t>Corrección</t>
@@ -1930,6 +2440,16 @@
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>Mar</t>
+        </is>
+      </c>
       <c r="C60" s="13" t="inlineStr">
         <is>
           <t>Corrección</t>
@@ -1952,6 +2472,16 @@
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>Mar</t>
+        </is>
+      </c>
       <c r="C61" s="13" t="inlineStr">
         <is>
           <t>Corrección</t>
@@ -1974,6 +2504,16 @@
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>Mar</t>
+        </is>
+      </c>
       <c r="C62" s="13" t="inlineStr">
         <is>
           <t>Corrección</t>
@@ -1996,6 +2536,16 @@
       </c>
     </row>
     <row r="63" ht="18" customHeight="1">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>Mar</t>
+        </is>
+      </c>
       <c r="C63" s="13" t="inlineStr">
         <is>
           <t>Corrección</t>
@@ -2050,6 +2600,16 @@
       </c>
     </row>
     <row r="65" ht="18" customHeight="1">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>Mié</t>
+        </is>
+      </c>
       <c r="C65" s="13" t="inlineStr">
         <is>
           <t>Corrección</t>
@@ -2072,6 +2632,16 @@
       </c>
     </row>
     <row r="66" ht="18" customHeight="1">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>Mié</t>
+        </is>
+      </c>
       <c r="C66" s="8" t="inlineStr">
         <is>
           <t>Nueva función</t>
@@ -2094,6 +2664,16 @@
       </c>
     </row>
     <row r="67" ht="18" customHeight="1">
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>Mié</t>
+        </is>
+      </c>
       <c r="C67" s="13" t="inlineStr">
         <is>
           <t>Corrección</t>
@@ -2116,6 +2696,16 @@
       </c>
     </row>
     <row r="68" ht="18" customHeight="1">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>Mié</t>
+        </is>
+      </c>
       <c r="C68" s="13" t="inlineStr">
         <is>
           <t>Corrección</t>
@@ -2138,6 +2728,16 @@
       </c>
     </row>
     <row r="69" ht="18" customHeight="1">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>Mié</t>
+        </is>
+      </c>
       <c r="C69" s="8" t="inlineStr">
         <is>
           <t>Nueva función</t>
@@ -2256,6 +2856,16 @@
       </c>
     </row>
     <row r="73" ht="18" customHeight="1">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>Lun</t>
+        </is>
+      </c>
       <c r="C73" s="13" t="inlineStr">
         <is>
           <t>Corrección</t>
@@ -2278,6 +2888,16 @@
       </c>
     </row>
     <row r="74" ht="18" customHeight="1">
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>Lun</t>
+        </is>
+      </c>
       <c r="C74" s="12" t="inlineStr">
         <is>
           <t>Mantenimiento</t>
@@ -2300,6 +2920,16 @@
       </c>
     </row>
     <row r="75" ht="18" customHeight="1">
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>Lun</t>
+        </is>
+      </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
           <t>Documentación</t>
@@ -2322,6 +2952,16 @@
       </c>
     </row>
     <row r="76" ht="18" customHeight="1">
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t>Lun</t>
+        </is>
+      </c>
       <c r="C76" s="13" t="inlineStr">
         <is>
           <t>Corrección</t>
@@ -2344,6 +2984,16 @@
       </c>
     </row>
     <row r="77" ht="18" customHeight="1">
+      <c r="A77" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="inlineStr">
+        <is>
+          <t>Lun</t>
+        </is>
+      </c>
       <c r="C77" s="13" t="inlineStr">
         <is>
           <t>Corrección</t>
@@ -2398,6 +3048,16 @@
       </c>
     </row>
     <row r="79" ht="18" customHeight="1">
+      <c r="A79" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>Mar</t>
+        </is>
+      </c>
       <c r="C79" s="13" t="inlineStr">
         <is>
           <t>Corrección</t>
@@ -2420,6 +3080,16 @@
       </c>
     </row>
     <row r="80" ht="18" customHeight="1">
+      <c r="A80" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t>Mar</t>
+        </is>
+      </c>
       <c r="C80" s="13" t="inlineStr">
         <is>
           <t>Corrección</t>
@@ -2442,6 +3112,16 @@
       </c>
     </row>
     <row r="81" ht="18" customHeight="1">
+      <c r="A81" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="inlineStr">
+        <is>
+          <t>Mar</t>
+        </is>
+      </c>
       <c r="C81" s="12" t="inlineStr">
         <is>
           <t>Mantenimiento</t>
@@ -2464,6 +3144,16 @@
       </c>
     </row>
     <row r="82" ht="18" customHeight="1">
+      <c r="A82" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>Mar</t>
+        </is>
+      </c>
       <c r="C82" s="12" t="inlineStr">
         <is>
           <t>Mantenimiento</t>
@@ -2514,6 +3204,16 @@
       </c>
     </row>
     <row r="84" ht="18" customHeight="1">
+      <c r="A84" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B84" s="3" t="inlineStr">
+        <is>
+          <t>Mié</t>
+        </is>
+      </c>
       <c r="C84" s="13" t="inlineStr">
         <is>
           <t>Corrección</t>
@@ -2546,316 +3246,510 @@
           <t>Jue</t>
         </is>
       </c>
-      <c r="C85" s="8" t="inlineStr">
+      <c r="C85" s="13" t="inlineStr">
+        <is>
+          <t>Corrección</t>
+        </is>
+      </c>
+      <c r="D85" s="5" t="inlineStr">
+        <is>
+          <t>repite Fecha/Día por fila — elimina merge_cells incompatible con Google Sheets</t>
+        </is>
+      </c>
+      <c r="E85" s="6" t="inlineStr">
+        <is>
+          <t>REPORT</t>
+        </is>
+      </c>
+      <c r="F85" s="7" t="inlineStr">
+        <is>
+          <t>Gerardo Herrera</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="18" customHeight="1">
+      <c r="A86" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="inlineStr">
+        <is>
+          <t>Jue</t>
+        </is>
+      </c>
+      <c r="C86" s="8" t="inlineStr">
         <is>
           <t>Nueva función</t>
         </is>
       </c>
-      <c r="D85" s="5" t="inlineStr">
+      <c r="D86" s="9" t="inlineStr">
         <is>
           <t>redistribuye cc-row — elimina cc-icon, nuevo cc-bottom con chip + botón</t>
         </is>
       </c>
-      <c r="E85" s="6" t="inlineStr">
+      <c r="E86" s="10" t="inlineStr">
         <is>
           <t>UI</t>
         </is>
       </c>
-      <c r="F85" s="7" t="inlineStr">
-        <is>
-          <t>Gerardo Herrera</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="18" customHeight="1">
-      <c r="C86" s="13" t="inlineStr">
-        <is>
-          <t>Corrección</t>
-        </is>
-      </c>
-      <c r="D86" s="9" t="inlineStr">
+      <c r="F86" s="11" t="inlineStr">
+        <is>
+          <t>Gerardo Herrera</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="18" customHeight="1">
+      <c r="A87" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B87" s="3" t="inlineStr">
+        <is>
+          <t>Jue</t>
+        </is>
+      </c>
+      <c r="C87" s="13" t="inlineStr">
+        <is>
+          <t>Corrección</t>
+        </is>
+      </c>
+      <c r="D87" s="5" t="inlineStr">
         <is>
           <t>ajusta pv-icon a translateY(10px)</t>
         </is>
       </c>
-      <c r="E86" s="10" t="inlineStr">
+      <c r="E87" s="6" t="inlineStr">
         <is>
           <t>UI</t>
         </is>
       </c>
-      <c r="F86" s="11" t="inlineStr">
-        <is>
-          <t>Gerardo Herrera</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="18" customHeight="1">
-      <c r="C87" s="13" t="inlineStr">
-        <is>
-          <t>Corrección</t>
-        </is>
-      </c>
-      <c r="D87" s="5" t="inlineStr">
+      <c r="F87" s="7" t="inlineStr">
+        <is>
+          <t>Gerardo Herrera</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="18" customHeight="1">
+      <c r="A88" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="inlineStr">
+        <is>
+          <t>Jue</t>
+        </is>
+      </c>
+      <c r="C88" s="13" t="inlineStr">
+        <is>
+          <t>Corrección</t>
+        </is>
+      </c>
+      <c r="D88" s="9" t="inlineStr">
         <is>
           <t>baja pv-icon 5px con translateY</t>
         </is>
       </c>
-      <c r="E87" s="6" t="inlineStr">
+      <c r="E88" s="10" t="inlineStr">
         <is>
           <t>UI</t>
         </is>
       </c>
-      <c r="F87" s="7" t="inlineStr">
-        <is>
-          <t>Gerardo Herrera</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="18" customHeight="1">
-      <c r="C88" s="13" t="inlineStr">
-        <is>
-          <t>Corrección</t>
-        </is>
-      </c>
-      <c r="D88" s="9" t="inlineStr">
+      <c r="F88" s="11" t="inlineStr">
+        <is>
+          <t>Gerardo Herrera</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="18" customHeight="1">
+      <c r="A89" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B89" s="3" t="inlineStr">
+        <is>
+          <t>Jue</t>
+        </is>
+      </c>
+      <c r="C89" s="13" t="inlineStr">
+        <is>
+          <t>Corrección</t>
+        </is>
+      </c>
+      <c r="D89" s="5" t="inlineStr">
         <is>
           <t>regresa pv-icon al centro y reduce cc-preview a 125px</t>
         </is>
       </c>
-      <c r="E88" s="10" t="inlineStr">
+      <c r="E89" s="6" t="inlineStr">
         <is>
           <t>UI</t>
         </is>
       </c>
-      <c r="F88" s="11" t="inlineStr">
-        <is>
-          <t>Gerardo Herrera</t>
-        </is>
-      </c>
-    </row>
-    <row r="89" ht="18" customHeight="1">
-      <c r="C89" s="8" t="inlineStr">
+      <c r="F89" s="7" t="inlineStr">
+        <is>
+          <t>Gerardo Herrera</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="18" customHeight="1">
+      <c r="A90" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B90" s="3" t="inlineStr">
+        <is>
+          <t>Jue</t>
+        </is>
+      </c>
+      <c r="C90" s="8" t="inlineStr">
         <is>
           <t>Nueva función</t>
         </is>
       </c>
-      <c r="D89" s="5" t="inlineStr">
+      <c r="D90" s="9" t="inlineStr">
         <is>
           <t>redistribuye elementos de cc-preview en catalog-card</t>
         </is>
       </c>
-      <c r="E89" s="6" t="inlineStr">
+      <c r="E90" s="10" t="inlineStr">
         <is>
           <t>UI</t>
         </is>
       </c>
-      <c r="F89" s="7" t="inlineStr">
-        <is>
-          <t>Gerardo Herrera</t>
-        </is>
-      </c>
-    </row>
-    <row r="90" ht="18" customHeight="1">
-      <c r="C90" s="12" t="inlineStr">
+      <c r="F90" s="11" t="inlineStr">
+        <is>
+          <t>Gerardo Herrera</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="18" customHeight="1">
+      <c r="A91" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B91" s="3" t="inlineStr">
+        <is>
+          <t>Jue</t>
+        </is>
+      </c>
+      <c r="C91" s="12" t="inlineStr">
         <is>
           <t>Mantenimiento</t>
         </is>
       </c>
-      <c r="D90" s="9" t="inlineStr">
+      <c r="D91" s="5" t="inlineStr">
         <is>
           <t>acepta REPO y OUT como argumentos CLI en generate_report.py</t>
         </is>
       </c>
-      <c r="E90" s="10" t="inlineStr">
+      <c r="E91" s="6" t="inlineStr">
         <is>
           <t>REPORTS</t>
         </is>
       </c>
-      <c r="F90" s="11" t="inlineStr">
-        <is>
-          <t>Gerardo Herrera</t>
-        </is>
-      </c>
-    </row>
-    <row r="91" ht="18" customHeight="1">
-      <c r="C91" s="13" t="inlineStr">
-        <is>
-          <t>Corrección</t>
-        </is>
-      </c>
-      <c r="D91" s="5" t="inlineStr">
+      <c r="F91" s="7" t="inlineStr">
+        <is>
+          <t>Gerardo Herrera</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="18" customHeight="1">
+      <c r="A92" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B92" s="3" t="inlineStr">
+        <is>
+          <t>Jue</t>
+        </is>
+      </c>
+      <c r="C92" s="13" t="inlineStr">
+        <is>
+          <t>Corrección</t>
+        </is>
+      </c>
+      <c r="D92" s="9" t="inlineStr">
         <is>
           <t>extrae 13 estilos tipográficos inline a clases CSS</t>
         </is>
       </c>
-      <c r="E91" s="6" t="inlineStr">
+      <c r="E92" s="10" t="inlineStr">
         <is>
           <t>UI</t>
         </is>
       </c>
-      <c r="F91" s="7" t="inlineStr">
-        <is>
-          <t>Gerardo Herrera</t>
-        </is>
-      </c>
-    </row>
-    <row r="92" ht="18" customHeight="1">
-      <c r="C92" s="13" t="inlineStr">
-        <is>
-          <t>Corrección</t>
-        </is>
-      </c>
-      <c r="D92" s="9" t="inlineStr">
+      <c r="F92" s="11" t="inlineStr">
+        <is>
+          <t>Gerardo Herrera</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="18" customHeight="1">
+      <c r="A93" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B93" s="3" t="inlineStr">
+        <is>
+          <t>Jue</t>
+        </is>
+      </c>
+      <c r="C93" s="13" t="inlineStr">
+        <is>
+          <t>Corrección</t>
+        </is>
+      </c>
+      <c r="D93" s="5" t="inlineStr">
         <is>
           <t>agrega line-height explícito a 4 elementos de texto multilinea</t>
         </is>
       </c>
-      <c r="E92" s="10" t="inlineStr">
+      <c r="E93" s="6" t="inlineStr">
         <is>
           <t>UI</t>
         </is>
       </c>
-      <c r="F92" s="11" t="inlineStr">
-        <is>
-          <t>Gerardo Herrera</t>
-        </is>
-      </c>
-    </row>
-    <row r="93" ht="18" customHeight="1">
-      <c r="C93" s="13" t="inlineStr">
-        <is>
-          <t>Corrección</t>
-        </is>
-      </c>
-      <c r="D93" s="5" t="inlineStr">
+      <c r="F93" s="7" t="inlineStr">
+        <is>
+          <t>Gerardo Herrera</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="18" customHeight="1">
+      <c r="A94" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B94" s="3" t="inlineStr">
+        <is>
+          <t>Jue</t>
+        </is>
+      </c>
+      <c r="C94" s="13" t="inlineStr">
+        <is>
+          <t>Corrección</t>
+        </is>
+      </c>
+      <c r="D94" s="9" t="inlineStr">
         <is>
           <t>agrega font-family a .cat-explore-head .row-eyebrow</t>
         </is>
       </c>
-      <c r="E93" s="6" t="inlineStr">
+      <c r="E94" s="10" t="inlineStr">
         <is>
           <t>UI</t>
         </is>
       </c>
-      <c r="F93" s="7" t="inlineStr">
-        <is>
-          <t>Gerardo Herrera</t>
-        </is>
-      </c>
-    </row>
-    <row r="94" ht="18" customHeight="1">
-      <c r="C94" s="13" t="inlineStr">
-        <is>
-          <t>Corrección</t>
-        </is>
-      </c>
-      <c r="D94" s="9" t="inlineStr">
+      <c r="F94" s="11" t="inlineStr">
+        <is>
+          <t>Gerardo Herrera</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="18" customHeight="1">
+      <c r="A95" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B95" s="3" t="inlineStr">
+        <is>
+          <t>Jue</t>
+        </is>
+      </c>
+      <c r="C95" s="13" t="inlineStr">
+        <is>
+          <t>Corrección</t>
+        </is>
+      </c>
+      <c r="D95" s="5" t="inlineStr">
         <is>
           <t>sube font-size de labels del gráfico analytics de 9px a 11px</t>
         </is>
       </c>
-      <c r="E94" s="10" t="inlineStr">
+      <c r="E95" s="6" t="inlineStr">
         <is>
           <t>UI</t>
         </is>
       </c>
-      <c r="F94" s="11" t="inlineStr">
-        <is>
-          <t>Gerardo Herrera</t>
-        </is>
-      </c>
-    </row>
-    <row r="95" ht="18" customHeight="1">
-      <c r="C95" s="13" t="inlineStr">
-        <is>
-          <t>Corrección</t>
-        </is>
-      </c>
-      <c r="D95" s="5" t="inlineStr">
+      <c r="F95" s="7" t="inlineStr">
+        <is>
+          <t>Gerardo Herrera</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="18" customHeight="1">
+      <c r="A96" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B96" s="3" t="inlineStr">
+        <is>
+          <t>Jue</t>
+        </is>
+      </c>
+      <c r="C96" s="13" t="inlineStr">
+        <is>
+          <t>Corrección</t>
+        </is>
+      </c>
+      <c r="D96" s="9" t="inlineStr">
         <is>
           <t>corrige letter-spacing de .login-card h1 a -.02em</t>
         </is>
       </c>
-      <c r="E95" s="6" t="inlineStr">
+      <c r="E96" s="10" t="inlineStr">
         <is>
           <t>UI</t>
         </is>
       </c>
-      <c r="F95" s="7" t="inlineStr">
-        <is>
-          <t>Gerardo Herrera</t>
-        </is>
-      </c>
-    </row>
-    <row r="96" ht="18" customHeight="1">
-      <c r="C96" s="13" t="inlineStr">
-        <is>
-          <t>Corrección</t>
-        </is>
-      </c>
-      <c r="D96" s="9" t="inlineStr">
+      <c r="F96" s="11" t="inlineStr">
+        <is>
+          <t>Gerardo Herrera</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="18" customHeight="1">
+      <c r="A97" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B97" s="3" t="inlineStr">
+        <is>
+          <t>Jue</t>
+        </is>
+      </c>
+      <c r="C97" s="13" t="inlineStr">
+        <is>
+          <t>Corrección</t>
+        </is>
+      </c>
+      <c r="D97" s="5" t="inlineStr">
         <is>
           <t>convierte letter-spacing de px a em en toda la hoja de estilos</t>
         </is>
       </c>
-      <c r="E96" s="10" t="inlineStr">
+      <c r="E97" s="6" t="inlineStr">
         <is>
           <t>UI</t>
         </is>
       </c>
-      <c r="F96" s="11" t="inlineStr">
-        <is>
-          <t>Gerardo Herrera</t>
-        </is>
-      </c>
-    </row>
-    <row r="97" ht="18" customHeight="1">
-      <c r="C97" s="13" t="inlineStr">
-        <is>
-          <t>Corrección</t>
-        </is>
-      </c>
-      <c r="D97" s="5" t="inlineStr">
+      <c r="F97" s="7" t="inlineStr">
+        <is>
+          <t>Gerardo Herrera</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="18" customHeight="1">
+      <c r="A98" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B98" s="3" t="inlineStr">
+        <is>
+          <t>Jue</t>
+        </is>
+      </c>
+      <c r="C98" s="13" t="inlineStr">
+        <is>
+          <t>Corrección</t>
+        </is>
+      </c>
+      <c r="D98" s="9" t="inlineStr">
         <is>
           <t>elimina definiciones CSS conflictivas — unifica escala tipográfica</t>
         </is>
       </c>
-      <c r="E97" s="6" t="inlineStr">
+      <c r="E98" s="10" t="inlineStr">
         <is>
           <t>UI</t>
         </is>
       </c>
-      <c r="F97" s="7" t="inlineStr">
+      <c r="F98" s="11" t="inlineStr">
+        <is>
+          <t>Gerardo Herrera</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="18" customHeight="1">
+      <c r="A99" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B99" s="3" t="inlineStr">
+        <is>
+          <t>Vie</t>
+        </is>
+      </c>
+      <c r="C99" s="13" t="inlineStr">
+        <is>
+          <t>Corrección</t>
+        </is>
+      </c>
+      <c r="D99" s="5" t="inlineStr">
+        <is>
+          <t>enriquece títulos consultando deploys de prod en QA</t>
+        </is>
+      </c>
+      <c r="E99" s="6" t="inlineStr">
+        <is>
+          <t>WEEKLY-REPORT</t>
+        </is>
+      </c>
+      <c r="F99" s="7" t="inlineStr">
+        <is>
+          <t>Gerardo Herrera</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="18" customHeight="1">
+      <c r="A100" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B100" s="3" t="inlineStr">
+        <is>
+          <t>Vie</t>
+        </is>
+      </c>
+      <c r="C100" s="8" t="inlineStr">
+        <is>
+          <t>Nueva función</t>
+        </is>
+      </c>
+      <c r="D100" s="9" t="inlineStr">
+        <is>
+          <t>reporte semanal automático con opt-in por app</t>
+        </is>
+      </c>
+      <c r="E100" s="10" t="inlineStr">
+        <is>
+          <t>WEEKLY-REPORT</t>
+        </is>
+      </c>
+      <c r="F100" s="11" t="inlineStr">
         <is>
           <t>Gerardo Herrera</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="23">
-    <mergeCell ref="A9:A23"/>
-    <mergeCell ref="B78:B82"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="A64:A69"/>
-    <mergeCell ref="A55:A63"/>
-    <mergeCell ref="B72:B77"/>
-    <mergeCell ref="A34:A54"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="A24:A33"/>
-    <mergeCell ref="A85:A97"/>
-    <mergeCell ref="B83:B84"/>
-    <mergeCell ref="B9:B23"/>
-    <mergeCell ref="B55:B63"/>
-    <mergeCell ref="A5:A8"/>
-    <mergeCell ref="B85:B97"/>
-    <mergeCell ref="B5:B8"/>
-    <mergeCell ref="A78:A82"/>
-    <mergeCell ref="B64:B69"/>
+  <mergeCells count="1">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="B34:B54"/>
-    <mergeCell ref="A83:A84"/>
-    <mergeCell ref="A72:A77"/>
-    <mergeCell ref="B24:B33"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2896,7 +3790,7 @@
         </is>
       </c>
       <c r="B3" s="19" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C3" s="20" t="inlineStr">
         <is>
@@ -2911,11 +3805,11 @@
         </is>
       </c>
       <c r="B4" s="19" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C4" s="20" t="inlineStr">
         <is>
-          <t>26%</t>
+          <t>27%</t>
         </is>
       </c>
     </row>
@@ -2930,7 +3824,7 @@
       </c>
       <c r="C5" s="20" t="inlineStr">
         <is>
-          <t>11%</t>
+          <t>10%</t>
         </is>
       </c>
     </row>
@@ -2986,7 +3880,7 @@
         </is>
       </c>
       <c r="B10" s="19" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
     </row>
     <row r="11">
@@ -2996,7 +3890,7 @@
         </is>
       </c>
       <c r="B11" s="19" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13">
@@ -3013,7 +3907,7 @@
         </is>
       </c>
       <c r="B14" s="19" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="15">

--- a/cambios_tinacode.xlsx
+++ b/cambios_tinacode.xlsx
@@ -581,7 +581,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F100"/>
+  <dimension ref="A1:F112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -595,7 +595,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Reporte de Cambios · TinaCode  —  2026-06-01 al 2026-06-20</t>
+          <t>Reporte de Cambios · TinaCode  —  2026-06-01 al 2026-06-23</t>
         </is>
       </c>
     </row>
@@ -3742,6 +3742,390 @@
         </is>
       </c>
       <c r="F100" s="11" t="inlineStr">
+        <is>
+          <t>Gerardo Herrera</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="18" customHeight="1">
+      <c r="A101" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B101" s="3" t="inlineStr">
+        <is>
+          <t>Lun</t>
+        </is>
+      </c>
+      <c r="C101" s="13" t="inlineStr">
+        <is>
+          <t>Corrección</t>
+        </is>
+      </c>
+      <c r="D101" s="5" t="inlineStr">
+        <is>
+          <t>cambia etiqueta ESTE MES a estilo amb-lbl</t>
+        </is>
+      </c>
+      <c r="E101" s="6" t="inlineStr">
+        <is>
+          <t>ADMIN</t>
+        </is>
+      </c>
+      <c r="F101" s="7" t="inlineStr">
+        <is>
+          <t>Gerardo Herrera</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="18" customHeight="1">
+      <c r="A102" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B102" s="3" t="inlineStr">
+        <is>
+          <t>Lun</t>
+        </is>
+      </c>
+      <c r="C102" s="13" t="inlineStr">
+        <is>
+          <t>Corrección</t>
+        </is>
+      </c>
+      <c r="D102" s="9" t="inlineStr">
+        <is>
+          <t>cambia etiqueta TOP por Top User con estilo amb-lbl</t>
+        </is>
+      </c>
+      <c r="E102" s="10" t="inlineStr">
+        <is>
+          <t>ADMIN</t>
+        </is>
+      </c>
+      <c r="F102" s="11" t="inlineStr">
+        <is>
+          <t>Gerardo Herrera</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="18" customHeight="1">
+      <c r="A103" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B103" s="3" t="inlineStr">
+        <is>
+          <t>Lun</t>
+        </is>
+      </c>
+      <c r="C103" s="13" t="inlineStr">
+        <is>
+          <t>Corrección</t>
+        </is>
+      </c>
+      <c r="D103" s="5" t="inlineStr">
+        <is>
+          <t>texto este mes y Top en mayúsculas en banda de métricas</t>
+        </is>
+      </c>
+      <c r="E103" s="6" t="inlineStr">
+        <is>
+          <t>ADMIN</t>
+        </is>
+      </c>
+      <c r="F103" s="7" t="inlineStr">
+        <is>
+          <t>Gerardo Herrera</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="18" customHeight="1">
+      <c r="A104" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B104" s="3" t="inlineStr">
+        <is>
+          <t>Lun</t>
+        </is>
+      </c>
+      <c r="C104" s="13" t="inlineStr">
+        <is>
+          <t>Corrección</t>
+        </is>
+      </c>
+      <c r="D104" s="9" t="inlineStr">
+        <is>
+          <t>elimina bloque Tipo Acceso de la banda de métricas</t>
+        </is>
+      </c>
+      <c r="E104" s="10" t="inlineStr">
+        <is>
+          <t>ADMIN</t>
+        </is>
+      </c>
+      <c r="F104" s="11" t="inlineStr">
+        <is>
+          <t>Gerardo Herrera</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="18" customHeight="1">
+      <c r="A105" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B105" s="3" t="inlineStr">
+        <is>
+          <t>Lun</t>
+        </is>
+      </c>
+      <c r="C105" s="13" t="inlineStr">
+        <is>
+          <t>Corrección</t>
+        </is>
+      </c>
+      <c r="D105" s="5" t="inlineStr">
+        <is>
+          <t>separa datos de QA y prod en admin stats y share tokens</t>
+        </is>
+      </c>
+      <c r="E105" s="6" t="inlineStr">
+        <is>
+          <t>DATA-ISOLATION</t>
+        </is>
+      </c>
+      <c r="F105" s="7" t="inlineStr">
+        <is>
+          <t>Gerardo Herrera</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="18" customHeight="1">
+      <c r="A106" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B106" s="3" t="inlineStr">
+        <is>
+          <t>Lun</t>
+        </is>
+      </c>
+      <c r="C106" s="13" t="inlineStr">
+        <is>
+          <t>Corrección</t>
+        </is>
+      </c>
+      <c r="D106" s="9" t="inlineStr">
+        <is>
+          <t>corrige título de app eliminada en banda de métricas</t>
+        </is>
+      </c>
+      <c r="E106" s="10" t="inlineStr">
+        <is>
+          <t>ADMIN</t>
+        </is>
+      </c>
+      <c r="F106" s="11" t="inlineStr">
+        <is>
+          <t>Gerardo Herrera</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="18" customHeight="1">
+      <c r="A107" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B107" s="3" t="inlineStr">
+        <is>
+          <t>Lun</t>
+        </is>
+      </c>
+      <c r="C107" s="13" t="inlineStr">
+        <is>
+          <t>Corrección</t>
+        </is>
+      </c>
+      <c r="D107" s="5" t="inlineStr">
+        <is>
+          <t>corrige título de app con más aperturas en banda de métricas</t>
+        </is>
+      </c>
+      <c r="E107" s="6" t="inlineStr">
+        <is>
+          <t>ADMIN</t>
+        </is>
+      </c>
+      <c r="F107" s="7" t="inlineStr">
+        <is>
+          <t>Gerardo Herrera</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="18" customHeight="1">
+      <c r="A108" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B108" s="3" t="inlineStr">
+        <is>
+          <t>Lun</t>
+        </is>
+      </c>
+      <c r="C108" s="8" t="inlineStr">
+        <is>
+          <t>Nueva función</t>
+        </is>
+      </c>
+      <c r="D108" s="9" t="inlineStr">
+        <is>
+          <t>agrega bloque 'App con más aperturas' en la banda de métricas</t>
+        </is>
+      </c>
+      <c r="E108" s="10" t="inlineStr">
+        <is>
+          <t>ADMIN</t>
+        </is>
+      </c>
+      <c r="F108" s="11" t="inlineStr">
+        <is>
+          <t>Gerardo Herrera</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="18" customHeight="1">
+      <c r="A109" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B109" s="3" t="inlineStr">
+        <is>
+          <t>Lun</t>
+        </is>
+      </c>
+      <c r="C109" s="13" t="inlineStr">
+        <is>
+          <t>Corrección</t>
+        </is>
+      </c>
+      <c r="D109" s="5" t="inlineStr">
+        <is>
+          <t>ajusta etiquetas y elimina sección Salud de la banda de métricas</t>
+        </is>
+      </c>
+      <c r="E109" s="6" t="inlineStr">
+        <is>
+          <t>ADMIN</t>
+        </is>
+      </c>
+      <c r="F109" s="7" t="inlineStr">
+        <is>
+          <t>Gerardo Herrera</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="18" customHeight="1">
+      <c r="A110" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B110" s="3" t="inlineStr">
+        <is>
+          <t>Lun</t>
+        </is>
+      </c>
+      <c r="C110" s="8" t="inlineStr">
+        <is>
+          <t>Nueva función</t>
+        </is>
+      </c>
+      <c r="D110" s="9" t="inlineStr">
+        <is>
+          <t>banda de métricas secundaria en panel admin</t>
+        </is>
+      </c>
+      <c r="E110" s="10" t="inlineStr">
+        <is>
+          <t>ADMIN</t>
+        </is>
+      </c>
+      <c r="F110" s="11" t="inlineStr">
+        <is>
+          <t>Gerardo Herrera</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="18" customHeight="1">
+      <c r="A111" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B111" s="3" t="inlineStr">
+        <is>
+          <t>Lun</t>
+        </is>
+      </c>
+      <c r="C111" s="13" t="inlineStr">
+        <is>
+          <t>Corrección</t>
+        </is>
+      </c>
+      <c r="D111" s="5" t="inlineStr">
+        <is>
+          <t>agrega traducción th_health en los tres idiomas</t>
+        </is>
+      </c>
+      <c r="E111" s="6" t="inlineStr">
+        <is>
+          <t>HEALTH-MONITOR</t>
+        </is>
+      </c>
+      <c r="F111" s="7" t="inlineStr">
+        <is>
+          <t>Gerardo Herrera</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="18" customHeight="1">
+      <c r="A112" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B112" s="3" t="inlineStr">
+        <is>
+          <t>Lun</t>
+        </is>
+      </c>
+      <c r="C112" s="8" t="inlineStr">
+        <is>
+          <t>Nueva función</t>
+        </is>
+      </c>
+      <c r="D112" s="9" t="inlineStr">
+        <is>
+          <t>monitor automático de salud de apps publicadas</t>
+        </is>
+      </c>
+      <c r="E112" s="10" t="inlineStr">
+        <is>
+          <t>HEALTH-MONITOR</t>
+        </is>
+      </c>
+      <c r="F112" s="11" t="inlineStr">
         <is>
           <t>Gerardo Herrera</t>
         </is>
@@ -3790,11 +4174,11 @@
         </is>
       </c>
       <c r="B3" s="19" t="n">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="C3" s="20" t="inlineStr">
         <is>
-          <t>59%</t>
+          <t>61%</t>
         </is>
       </c>
     </row>
@@ -3805,11 +4189,11 @@
         </is>
       </c>
       <c r="B4" s="19" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C4" s="20" t="inlineStr">
         <is>
-          <t>27%</t>
+          <t>26%</t>
         </is>
       </c>
     </row>
@@ -3824,7 +4208,7 @@
       </c>
       <c r="C5" s="20" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>9%</t>
         </is>
       </c>
     </row>
@@ -3880,7 +4264,7 @@
         </is>
       </c>
       <c r="B10" s="19" t="n">
-        <v>98</v>
+        <v>110</v>
       </c>
     </row>
     <row r="11">
@@ -3890,7 +4274,7 @@
         </is>
       </c>
       <c r="B11" s="19" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13">
@@ -3907,7 +4291,7 @@
         </is>
       </c>
       <c r="B14" s="19" t="n">
-        <v>96</v>
+        <v>108</v>
       </c>
     </row>
     <row r="15">
